--- a/research/traditional_assets/database/data/luxembourg/luxembourg_telecom_wireless.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_telecom_wireless.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07334929072204936</v>
+        <v>0.07320013459098856</v>
       </c>
       <c r="C2">
-        <v>11061.21511466715</v>
+        <v>10956.51460918249</v>
       </c>
       <c r="D2">
-        <v>10258.21511466715</v>
+        <v>10270.02660918249</v>
       </c>
       <c r="E2">
-        <v>-7362</v>
+        <v>-7245.488</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>116.512</v>
       </c>
       <c r="G2">
         <v>803</v>
@@ -1445,28 +1445,28 @@
         <v>1700</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>5.8605536</v>
       </c>
       <c r="N2">
-        <v>1700</v>
+        <v>1694.1394464</v>
       </c>
       <c r="O2">
-        <v>423.98</v>
+        <v>422.51837793216</v>
       </c>
       <c r="P2">
-        <v>1276.02</v>
+        <v>1271.62106846784</v>
       </c>
       <c r="Q2">
-        <v>2556.02</v>
+        <v>2551.62106846784</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07334929072204936</v>
+        <v>0.07355816443534198</v>
       </c>
       <c r="T2">
-        <v>0.6362422799549506</v>
+        <v>0.6410661532411545</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>290.0749854075219</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.07320013459098856</v>
+        <v>0.07305097845992778</v>
       </c>
       <c r="C3">
-        <v>10956.51460918249</v>
+        <v>10851.84133498948</v>
       </c>
       <c r="D3">
-        <v>10270.02660918249</v>
+        <v>10281.86533498948</v>
       </c>
       <c r="E3">
-        <v>-7245.488</v>
+        <v>-7128.976</v>
       </c>
       <c r="F3">
-        <v>116.512</v>
+        <v>233.024</v>
       </c>
       <c r="G3">
         <v>803</v>
@@ -1527,28 +1527,28 @@
         <v>1700</v>
       </c>
       <c r="M3">
-        <v>5.8605536</v>
+        <v>11.7211072</v>
       </c>
       <c r="N3">
-        <v>1694.1394464</v>
+        <v>1688.2788928</v>
       </c>
       <c r="O3">
-        <v>422.51837793216</v>
+        <v>421.05675586432</v>
       </c>
       <c r="P3">
-        <v>1271.62106846784</v>
+        <v>1267.22213693568</v>
       </c>
       <c r="Q3">
-        <v>2551.62106846784</v>
+        <v>2547.22213693568</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.07355816443534198</v>
+        <v>0.07377130087747732</v>
       </c>
       <c r="T3">
-        <v>0.6410661532411545</v>
+        <v>0.6459884729209544</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>290.0749854075219</v>
+        <v>145.037492703761</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07305097845992778</v>
+        <v>0.07290182232886698</v>
       </c>
       <c r="C4">
-        <v>10851.84133498948</v>
+        <v>10747.19538636905</v>
       </c>
       <c r="D4">
-        <v>10281.86533498948</v>
+        <v>10293.73138636905</v>
       </c>
       <c r="E4">
-        <v>-7128.976</v>
+        <v>-7012.464</v>
       </c>
       <c r="F4">
-        <v>233.024</v>
+        <v>349.536</v>
       </c>
       <c r="G4">
         <v>803</v>
@@ -1609,28 +1609,28 @@
         <v>1700</v>
       </c>
       <c r="M4">
-        <v>11.7211072</v>
+        <v>17.5816608</v>
       </c>
       <c r="N4">
-        <v>1688.2788928</v>
+        <v>1682.4183392</v>
       </c>
       <c r="O4">
-        <v>421.05675586432</v>
+        <v>419.59513379648</v>
       </c>
       <c r="P4">
-        <v>1267.22213693568</v>
+        <v>1262.82320540352</v>
       </c>
       <c r="Q4">
-        <v>2547.22213693568</v>
+        <v>2542.82320540352</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07377130087747732</v>
+        <v>0.07398883188542987</v>
       </c>
       <c r="T4">
-        <v>0.6459884729209544</v>
+        <v>0.6510122837281728</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>145.037492703761</v>
+        <v>96.69166180250731</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07290182232886698</v>
+        <v>0.0727526661978062</v>
       </c>
       <c r="C5">
-        <v>10747.19538636905</v>
+        <v>10642.57685803784</v>
       </c>
       <c r="D5">
-        <v>10293.73138636905</v>
+        <v>10305.62485803784</v>
       </c>
       <c r="E5">
-        <v>-7012.464</v>
+        <v>-6895.952</v>
       </c>
       <c r="F5">
-        <v>349.536</v>
+        <v>466.0480000000001</v>
       </c>
       <c r="G5">
         <v>803</v>
@@ -1691,28 +1691,28 @@
         <v>1700</v>
       </c>
       <c r="M5">
-        <v>17.5816608</v>
+        <v>23.4422144</v>
       </c>
       <c r="N5">
-        <v>1682.4183392</v>
+        <v>1676.5577856</v>
       </c>
       <c r="O5">
-        <v>419.59513379648</v>
+        <v>418.13351172864</v>
       </c>
       <c r="P5">
-        <v>1262.82320540352</v>
+        <v>1258.42427387136</v>
       </c>
       <c r="Q5">
-        <v>2542.82320540352</v>
+        <v>2538.42427387136</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07398883188542987</v>
+        <v>0.07421089478938145</v>
       </c>
       <c r="T5">
-        <v>0.6510122837281728</v>
+        <v>0.6561407572605417</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>96.69166180250731</v>
+        <v>72.51874635188048</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0727526661978062</v>
+        <v>0.0726035100667454</v>
       </c>
       <c r="C6">
-        <v>10642.57685803784</v>
+        <v>10537.98584515075</v>
       </c>
       <c r="D6">
-        <v>10305.62485803784</v>
+        <v>10317.54584515075</v>
       </c>
       <c r="E6">
-        <v>-6895.952</v>
+        <v>-6779.44</v>
       </c>
       <c r="F6">
-        <v>466.0480000000001</v>
+        <v>582.5600000000001</v>
       </c>
       <c r="G6">
         <v>803</v>
@@ -1773,28 +1773,28 @@
         <v>1700</v>
       </c>
       <c r="M6">
-        <v>23.4422144</v>
+        <v>29.302768</v>
       </c>
       <c r="N6">
-        <v>1676.5577856</v>
+        <v>1670.697232</v>
       </c>
       <c r="O6">
-        <v>418.13351172864</v>
+        <v>416.6718896608</v>
       </c>
       <c r="P6">
-        <v>1258.42427387136</v>
+        <v>1254.0253423392</v>
       </c>
       <c r="Q6">
-        <v>2538.42427387136</v>
+        <v>2534.0253423392</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07421089478938145</v>
+        <v>0.07443763270183726</v>
       </c>
       <c r="T6">
-        <v>0.6561407572605417</v>
+        <v>0.6613771986567499</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>72.51874635188048</v>
+        <v>58.01499708150438</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0726035100667454</v>
+        <v>0.07245435393568461</v>
       </c>
       <c r="C7">
-        <v>10537.98584515075</v>
+        <v>10433.42244330349</v>
       </c>
       <c r="D7">
-        <v>10317.54584515075</v>
+        <v>10329.49444330349</v>
       </c>
       <c r="E7">
-        <v>-6779.44</v>
+        <v>-6662.928</v>
       </c>
       <c r="F7">
-        <v>582.5600000000001</v>
+        <v>699.0720000000001</v>
       </c>
       <c r="G7">
         <v>803</v>
@@ -1855,28 +1855,28 @@
         <v>1700</v>
       </c>
       <c r="M7">
-        <v>29.302768</v>
+        <v>35.1633216</v>
       </c>
       <c r="N7">
-        <v>1670.697232</v>
+        <v>1664.8366784</v>
       </c>
       <c r="O7">
-        <v>416.6718896608</v>
+        <v>415.21026759296</v>
       </c>
       <c r="P7">
-        <v>1254.0253423392</v>
+        <v>1249.62641080704</v>
       </c>
       <c r="Q7">
-        <v>2534.0253423392</v>
+        <v>2529.62641080704</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07443763270183726</v>
+        <v>0.07466919482519639</v>
       </c>
       <c r="T7">
-        <v>0.6613771986567499</v>
+        <v>0.6667250536996858</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>58.01499708150438</v>
+        <v>48.34583090125365</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07245435393568461</v>
+        <v>0.07230519780462383</v>
       </c>
       <c r="C8">
-        <v>10433.42244330349</v>
+        <v>10328.88674853509</v>
       </c>
       <c r="D8">
-        <v>10329.49444330349</v>
+        <v>10341.47074853509</v>
       </c>
       <c r="E8">
-        <v>-6662.928</v>
+        <v>-6546.416</v>
       </c>
       <c r="F8">
-        <v>699.072</v>
+        <v>815.5839999999999</v>
       </c>
       <c r="G8">
         <v>803</v>
@@ -1937,28 +1937,28 @@
         <v>1700</v>
       </c>
       <c r="M8">
-        <v>35.1633216</v>
+        <v>41.02387519999999</v>
       </c>
       <c r="N8">
-        <v>1664.8366784</v>
+        <v>1658.9761248</v>
       </c>
       <c r="O8">
-        <v>415.21026759296</v>
+        <v>413.74864552512</v>
       </c>
       <c r="P8">
-        <v>1249.62641080704</v>
+        <v>1245.22747927488</v>
       </c>
       <c r="Q8">
-        <v>2529.62641080704</v>
+        <v>2525.22747927488</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07466919482519639</v>
+        <v>0.0749057367791654</v>
       </c>
       <c r="T8">
-        <v>0.6667250536996858</v>
+        <v>0.6721879163779539</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>48.34583090125366</v>
+        <v>41.43928362964599</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07230519780462383</v>
+        <v>0.07215604167356304</v>
       </c>
       <c r="C9">
-        <v>10328.88674853509</v>
+        <v>10224.37885733051</v>
       </c>
       <c r="D9">
-        <v>10341.47074853509</v>
+        <v>10353.47485733051</v>
       </c>
       <c r="E9">
-        <v>-6546.416</v>
+        <v>-6429.904</v>
       </c>
       <c r="F9">
-        <v>815.5840000000002</v>
+        <v>932.0960000000001</v>
       </c>
       <c r="G9">
         <v>803</v>
@@ -2019,28 +2019,28 @@
         <v>1700</v>
       </c>
       <c r="M9">
-        <v>41.02387520000001</v>
+        <v>46.8844288</v>
       </c>
       <c r="N9">
-        <v>1658.9761248</v>
+        <v>1653.1155712</v>
       </c>
       <c r="O9">
-        <v>413.74864552512</v>
+        <v>412.28702345728</v>
       </c>
       <c r="P9">
-        <v>1245.22747927488</v>
+        <v>1240.82854774272</v>
       </c>
       <c r="Q9">
-        <v>2525.22747927488</v>
+        <v>2520.82854774272</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0749057367791654</v>
+        <v>0.07514742094952503</v>
       </c>
       <c r="T9">
-        <v>0.6721879163779539</v>
+        <v>0.6777695369405321</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>41.43928362964598</v>
+        <v>36.25937317594024</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07215604167356304</v>
+        <v>0.07200688554250224</v>
       </c>
       <c r="C10">
-        <v>10224.37885733051</v>
+        <v>10119.89886662321</v>
       </c>
       <c r="D10">
-        <v>10353.47485733051</v>
+        <v>10365.50686662321</v>
       </c>
       <c r="E10">
-        <v>-6429.904</v>
+        <v>-6313.392</v>
       </c>
       <c r="F10">
-        <v>932.0960000000001</v>
+        <v>1048.608</v>
       </c>
       <c r="G10">
         <v>803</v>
@@ -2101,28 +2101,28 @@
         <v>1700</v>
       </c>
       <c r="M10">
-        <v>46.8844288</v>
+        <v>52.7449824</v>
       </c>
       <c r="N10">
-        <v>1653.1155712</v>
+        <v>1647.2550176</v>
       </c>
       <c r="O10">
-        <v>412.28702345728</v>
+        <v>410.82540138944</v>
       </c>
       <c r="P10">
-        <v>1240.82854774272</v>
+        <v>1236.42961621056</v>
       </c>
       <c r="Q10">
-        <v>2520.82854774272</v>
+        <v>2516.42961621056</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07514742094952503</v>
+        <v>0.07539441685989257</v>
       </c>
       <c r="T10">
-        <v>0.6777695369405321</v>
+        <v>0.6834738304825075</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.25937317594024</v>
+        <v>32.2305539341691</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07200688554250224</v>
+        <v>0.07185772941144146</v>
       </c>
       <c r="C11">
-        <v>10119.89886662321</v>
+        <v>10015.44687379778</v>
       </c>
       <c r="D11">
-        <v>10365.50686662321</v>
+        <v>10377.56687379778</v>
       </c>
       <c r="E11">
-        <v>-6313.392</v>
+        <v>-6196.88</v>
       </c>
       <c r="F11">
-        <v>1048.608</v>
+        <v>1165.12</v>
       </c>
       <c r="G11">
         <v>803</v>
@@ -2183,28 +2183,28 @@
         <v>1700</v>
       </c>
       <c r="M11">
-        <v>52.7449824</v>
+        <v>58.60553599999999</v>
       </c>
       <c r="N11">
-        <v>1647.2550176</v>
+        <v>1641.394464</v>
       </c>
       <c r="O11">
-        <v>410.82540138944</v>
+        <v>409.3637793216</v>
       </c>
       <c r="P11">
-        <v>1236.42961621056</v>
+        <v>1232.0306846784</v>
       </c>
       <c r="Q11">
-        <v>2516.42961621056</v>
+        <v>2512.0306846784</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07539441685989257</v>
+        <v>0.07564690156826828</v>
       </c>
       <c r="T11">
-        <v>0.6834738304825075</v>
+        <v>0.6893048861031935</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.2305539341691</v>
+        <v>29.0074985407522</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07185772941144146</v>
+        <v>0.07170857328038066</v>
       </c>
       <c r="C12">
-        <v>10015.44687379778</v>
+        <v>9911.022976692564</v>
       </c>
       <c r="D12">
-        <v>10377.56687379778</v>
+        <v>10389.65497669256</v>
       </c>
       <c r="E12">
-        <v>-6196.88</v>
+        <v>-6080.368</v>
       </c>
       <c r="F12">
-        <v>1165.12</v>
+        <v>1281.632</v>
       </c>
       <c r="G12">
         <v>803</v>
@@ -2265,28 +2265,28 @@
         <v>1700</v>
       </c>
       <c r="M12">
-        <v>58.605536</v>
+        <v>64.4660896</v>
       </c>
       <c r="N12">
-        <v>1641.394464</v>
+        <v>1635.5339104</v>
       </c>
       <c r="O12">
-        <v>409.3637793216</v>
+        <v>407.90215725376</v>
       </c>
       <c r="P12">
-        <v>1232.0306846784</v>
+        <v>1227.63175314624</v>
       </c>
       <c r="Q12">
-        <v>2512.0306846784</v>
+        <v>2507.63175314624</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07564690156826828</v>
+        <v>0.07590506009031533</v>
       </c>
       <c r="T12">
-        <v>0.6893048861031935</v>
+        <v>0.6952669766816477</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.00749854075219</v>
+        <v>26.37045321886563</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07170857328038066</v>
+        <v>0.07155941714931985</v>
       </c>
       <c r="C13">
-        <v>9911.022976692564</v>
+        <v>9806.627273602269</v>
       </c>
       <c r="D13">
-        <v>10389.65497669256</v>
+        <v>10401.77127360227</v>
       </c>
       <c r="E13">
-        <v>-6080.368</v>
+        <v>-5963.856</v>
       </c>
       <c r="F13">
-        <v>1281.632</v>
+        <v>1398.144</v>
       </c>
       <c r="G13">
         <v>803</v>
@@ -2347,28 +2347,28 @@
         <v>1700</v>
       </c>
       <c r="M13">
-        <v>64.4660896</v>
+        <v>70.32664319999999</v>
       </c>
       <c r="N13">
-        <v>1635.5339104</v>
+        <v>1629.6733568</v>
       </c>
       <c r="O13">
-        <v>407.90215725376</v>
+        <v>406.44053518592</v>
       </c>
       <c r="P13">
-        <v>1227.63175314624</v>
+        <v>1223.23282161408</v>
       </c>
       <c r="Q13">
-        <v>2507.63175314624</v>
+        <v>2503.23282161408</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07590506009031533</v>
+        <v>0.07616908585149984</v>
       </c>
       <c r="T13">
-        <v>0.6952669766816477</v>
+        <v>0.7013645693187032</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.37045321886563</v>
+        <v>24.17291545062683</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07155941714931985</v>
+        <v>0.07141026101825908</v>
       </c>
       <c r="C14">
-        <v>9806.627273602269</v>
+        <v>9702.259863280678</v>
       </c>
       <c r="D14">
-        <v>10401.77127360227</v>
+        <v>10413.91586328068</v>
       </c>
       <c r="E14">
-        <v>-5963.856</v>
+        <v>-5847.344</v>
       </c>
       <c r="F14">
-        <v>1398.144</v>
+        <v>1514.656</v>
       </c>
       <c r="G14">
         <v>803</v>
@@ -2429,28 +2429,28 @@
         <v>1700</v>
       </c>
       <c r="M14">
-        <v>70.32664319999999</v>
+        <v>76.18719680000001</v>
       </c>
       <c r="N14">
-        <v>1629.6733568</v>
+        <v>1623.8128032</v>
       </c>
       <c r="O14">
-        <v>406.44053518592</v>
+        <v>404.97891311808</v>
       </c>
       <c r="P14">
-        <v>1223.23282161408</v>
+        <v>1218.83389008192</v>
       </c>
       <c r="Q14">
-        <v>2503.23282161408</v>
+        <v>2498.83389008192</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07616908585149984</v>
+        <v>0.07643918117041273</v>
       </c>
       <c r="T14">
-        <v>0.7013645693187032</v>
+        <v>0.7076023364991394</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.17291545062683</v>
+        <v>22.31346041596322</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07141026101825908</v>
+        <v>0.07126110488719828</v>
       </c>
       <c r="C15">
-        <v>9702.259863280678</v>
+        <v>9597.920844943317</v>
       </c>
       <c r="D15">
-        <v>10413.91586328068</v>
+        <v>10426.08884494332</v>
       </c>
       <c r="E15">
-        <v>-5847.344</v>
+        <v>-5730.831999999999</v>
       </c>
       <c r="F15">
-        <v>1514.656</v>
+        <v>1631.168</v>
       </c>
       <c r="G15">
         <v>803</v>
@@ -2511,28 +2511,28 @@
         <v>1700</v>
       </c>
       <c r="M15">
-        <v>76.18719680000001</v>
+        <v>82.04775040000001</v>
       </c>
       <c r="N15">
-        <v>1623.8128032</v>
+        <v>1617.9522496</v>
       </c>
       <c r="O15">
-        <v>404.97891311808</v>
+        <v>403.51729105024</v>
       </c>
       <c r="P15">
-        <v>1218.83389008192</v>
+        <v>1214.43495854976</v>
       </c>
       <c r="Q15">
-        <v>2498.83389008192</v>
+        <v>2494.43495854976</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07643918117041273</v>
+        <v>0.07671555777581196</v>
       </c>
       <c r="T15">
-        <v>0.7076023364991394</v>
+        <v>0.7139851680326089</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.31346041596322</v>
+        <v>20.71964181482299</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07126110488719828</v>
+        <v>0.07111194875613748</v>
       </c>
       <c r="C16">
-        <v>9597.920844943317</v>
+        <v>9493.610318270137</v>
       </c>
       <c r="D16">
-        <v>10426.08884494332</v>
+        <v>10438.29031827014</v>
       </c>
       <c r="E16">
-        <v>-5730.831999999999</v>
+        <v>-5614.32</v>
       </c>
       <c r="F16">
-        <v>1631.168</v>
+        <v>1747.68</v>
       </c>
       <c r="G16">
         <v>803</v>
@@ -2593,28 +2593,28 @@
         <v>1700</v>
       </c>
       <c r="M16">
-        <v>82.04775040000001</v>
+        <v>87.90830400000002</v>
       </c>
       <c r="N16">
-        <v>1617.9522496</v>
+        <v>1612.091696</v>
       </c>
       <c r="O16">
-        <v>403.51729105024</v>
+        <v>402.0556689824</v>
       </c>
       <c r="P16">
-        <v>1214.43495854976</v>
+        <v>1210.0360270176</v>
       </c>
       <c r="Q16">
-        <v>2494.43495854976</v>
+        <v>2490.0360270176</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07671555777581196</v>
+        <v>0.07699843736016175</v>
       </c>
       <c r="T16">
-        <v>0.7139851680326089</v>
+        <v>0.720518183837454</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>20.71964181482299</v>
+        <v>19.33833236050146</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07111194875613748</v>
+        <v>0.0709627926250767</v>
       </c>
       <c r="C17">
-        <v>9493.610318270137</v>
+        <v>9389.328383408263</v>
       </c>
       <c r="D17">
-        <v>10438.29031827014</v>
+        <v>10450.52038340826</v>
       </c>
       <c r="E17">
-        <v>-5614.32</v>
+        <v>-5497.808</v>
       </c>
       <c r="F17">
-        <v>1747.68</v>
+        <v>1864.192</v>
       </c>
       <c r="G17">
         <v>803</v>
@@ -2675,28 +2675,28 @@
         <v>1700</v>
       </c>
       <c r="M17">
-        <v>87.908304</v>
+        <v>93.7688576</v>
       </c>
       <c r="N17">
-        <v>1612.091696</v>
+        <v>1606.2311424</v>
       </c>
       <c r="O17">
-        <v>402.0556689824</v>
+        <v>400.59404691456</v>
       </c>
       <c r="P17">
-        <v>1210.0360270176</v>
+        <v>1205.63709548544</v>
       </c>
       <c r="Q17">
-        <v>2490.0360270176</v>
+        <v>2485.63709548544</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07699843736016175</v>
+        <v>0.07728805217271036</v>
       </c>
       <c r="T17">
-        <v>0.720518183837454</v>
+        <v>0.7272067476376527</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.33833236050146</v>
+        <v>18.12968658797012</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0709627926250767</v>
+        <v>0.0708136364940159</v>
       </c>
       <c r="C18">
-        <v>9389.328383408263</v>
+        <v>9285.075140974719</v>
       </c>
       <c r="D18">
-        <v>10450.52038340826</v>
+        <v>10462.77914097472</v>
       </c>
       <c r="E18">
-        <v>-5497.808</v>
+        <v>-5381.296</v>
       </c>
       <c r="F18">
-        <v>1864.192</v>
+        <v>1980.704</v>
       </c>
       <c r="G18">
         <v>803</v>
@@ -2757,28 +2757,28 @@
         <v>1700</v>
       </c>
       <c r="M18">
-        <v>93.7688576</v>
+        <v>99.62941120000001</v>
       </c>
       <c r="N18">
-        <v>1606.2311424</v>
+        <v>1600.3705888</v>
       </c>
       <c r="O18">
-        <v>400.59404691456</v>
+        <v>399.13242484672</v>
       </c>
       <c r="P18">
-        <v>1205.63709548544</v>
+        <v>1201.23816395328</v>
       </c>
       <c r="Q18">
-        <v>2485.63709548544</v>
+        <v>2481.23816395328</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07728805217271036</v>
+        <v>0.07758464565544085</v>
       </c>
       <c r="T18">
-        <v>0.7272067476376527</v>
+        <v>0.7340564816499044</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.12968658797012</v>
+        <v>17.06323443573658</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0708136364940159</v>
+        <v>0.07066448036295511</v>
       </c>
       <c r="C19">
-        <v>9285.075140974719</v>
+        <v>9180.850692059188</v>
       </c>
       <c r="D19">
-        <v>10462.77914097472</v>
+        <v>10475.06669205919</v>
       </c>
       <c r="E19">
-        <v>-5381.296</v>
+        <v>-5264.784</v>
       </c>
       <c r="F19">
-        <v>1980.704</v>
+        <v>2097.216</v>
       </c>
       <c r="G19">
         <v>803</v>
@@ -2839,28 +2839,28 @@
         <v>1700</v>
       </c>
       <c r="M19">
-        <v>99.62941120000001</v>
+        <v>105.4899648</v>
       </c>
       <c r="N19">
-        <v>1600.3705888</v>
+        <v>1594.5100352</v>
       </c>
       <c r="O19">
-        <v>399.13242484672</v>
+        <v>397.67080277888</v>
       </c>
       <c r="P19">
-        <v>1201.23816395328</v>
+        <v>1196.83923242112</v>
       </c>
       <c r="Q19">
-        <v>2481.23816395328</v>
+        <v>2476.83923242112</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.07758464565544085</v>
+        <v>0.07788847312555502</v>
       </c>
       <c r="T19">
-        <v>0.7340564816499044</v>
+        <v>0.7410732823453817</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.06323443573658</v>
+        <v>16.11527696708455</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07066448036295513</v>
+        <v>0.07051532423189434</v>
       </c>
       <c r="C20">
-        <v>9180.850692059186</v>
+        <v>9076.65513822679</v>
       </c>
       <c r="D20">
-        <v>10475.06669205919</v>
+        <v>10487.38313822679</v>
       </c>
       <c r="E20">
-        <v>-5264.784</v>
+        <v>-5148.272</v>
       </c>
       <c r="F20">
-        <v>2097.216</v>
+        <v>2213.728</v>
       </c>
       <c r="G20">
         <v>803</v>
@@ -2921,28 +2921,28 @@
         <v>1700</v>
       </c>
       <c r="M20">
-        <v>105.4899648</v>
+        <v>111.3505184</v>
       </c>
       <c r="N20">
-        <v>1594.5100352</v>
+        <v>1588.6494816</v>
       </c>
       <c r="O20">
-        <v>397.67080277888</v>
+        <v>396.20918071104</v>
       </c>
       <c r="P20">
-        <v>1196.83923242112</v>
+        <v>1192.44030088896</v>
       </c>
       <c r="Q20">
-        <v>2476.83923242112</v>
+        <v>2472.44030088896</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.07788847312555502</v>
+        <v>0.07819980250851152</v>
       </c>
       <c r="T20">
-        <v>0.7410732823453817</v>
+        <v>0.748263337379019</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.11527696708455</v>
+        <v>15.26710449513273</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07051532423189434</v>
+        <v>0.07036616810083354</v>
       </c>
       <c r="C21">
-        <v>9076.65513822679</v>
+        <v>8972.488581520895</v>
       </c>
       <c r="D21">
-        <v>10487.38313822679</v>
+        <v>10499.72858152089</v>
       </c>
       <c r="E21">
-        <v>-5148.272</v>
+        <v>-5031.76</v>
       </c>
       <c r="F21">
-        <v>2213.728</v>
+        <v>2330.24</v>
       </c>
       <c r="G21">
         <v>803</v>
@@ -3003,28 +3003,28 @@
         <v>1700</v>
       </c>
       <c r="M21">
-        <v>111.3505184</v>
+        <v>117.211072</v>
       </c>
       <c r="N21">
-        <v>1588.6494816</v>
+        <v>1582.788928</v>
       </c>
       <c r="O21">
-        <v>396.20918071104</v>
+        <v>394.7475586432</v>
       </c>
       <c r="P21">
-        <v>1192.44030088896</v>
+        <v>1188.0413693568</v>
       </c>
       <c r="Q21">
-        <v>2472.44030088896</v>
+        <v>2468.0413693568</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.07819980250851152</v>
+        <v>0.07851891512604192</v>
       </c>
       <c r="T21">
-        <v>0.748263337379019</v>
+        <v>0.7556331437884972</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.26710449513273</v>
+        <v>14.5037492703761</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07036616810083354</v>
+        <v>0.07021701196977276</v>
       </c>
       <c r="C22">
-        <v>8972.488581520895</v>
+        <v>8868.351124465913</v>
       </c>
       <c r="D22">
-        <v>10499.72858152089</v>
+        <v>10512.10312446591</v>
       </c>
       <c r="E22">
-        <v>-5031.76</v>
+        <v>-4915.248</v>
       </c>
       <c r="F22">
-        <v>2330.24</v>
+        <v>2446.752</v>
       </c>
       <c r="G22">
         <v>803</v>
@@ -3085,28 +3085,28 @@
         <v>1700</v>
       </c>
       <c r="M22">
-        <v>117.211072</v>
+        <v>123.0716256</v>
       </c>
       <c r="N22">
-        <v>1582.788928</v>
+        <v>1576.9283744</v>
       </c>
       <c r="O22">
-        <v>394.7475586432</v>
+        <v>393.28593657536</v>
       </c>
       <c r="P22">
-        <v>1188.0413693568</v>
+        <v>1183.64243782464</v>
       </c>
       <c r="Q22">
-        <v>2468.0413693568</v>
+        <v>2463.64243782464</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.07851891512604192</v>
+        <v>0.07884610654401614</v>
       </c>
       <c r="T22">
-        <v>0.7556331437884972</v>
+        <v>0.7631895275754305</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.5037492703761</v>
+        <v>13.81309454321533</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07021701196977276</v>
+        <v>0.07006785583871195</v>
       </c>
       <c r="C23">
-        <v>8868.351124465913</v>
+        <v>8764.242870070164</v>
       </c>
       <c r="D23">
-        <v>10512.10312446591</v>
+        <v>10524.50687007016</v>
       </c>
       <c r="E23">
-        <v>-4915.248</v>
+        <v>-4798.736</v>
       </c>
       <c r="F23">
-        <v>2446.752</v>
+        <v>2563.264</v>
       </c>
       <c r="G23">
         <v>803</v>
@@ -3167,28 +3167,28 @@
         <v>1700</v>
       </c>
       <c r="M23">
-        <v>123.0716256</v>
+        <v>128.9321792</v>
       </c>
       <c r="N23">
-        <v>1576.9283744</v>
+        <v>1571.0678208</v>
       </c>
       <c r="O23">
-        <v>393.28593657536</v>
+        <v>391.82431450752</v>
       </c>
       <c r="P23">
-        <v>1183.64243782464</v>
+        <v>1179.24350629248</v>
       </c>
       <c r="Q23">
-        <v>2463.64243782464</v>
+        <v>2459.24350629248</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.07884610654401614</v>
+        <v>0.07918168748552815</v>
       </c>
       <c r="T23">
-        <v>0.7631895275754305</v>
+        <v>0.770939664792798</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>13.81309454321533</v>
+        <v>13.18522660943281</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07006785583871195</v>
+        <v>0.07017765670765116</v>
       </c>
       <c r="C24">
-        <v>8764.242870070164</v>
+        <v>8638.597047108555</v>
       </c>
       <c r="D24">
-        <v>10524.50687007016</v>
+        <v>10515.37304710855</v>
       </c>
       <c r="E24">
-        <v>-4798.736</v>
+        <v>-4682.224</v>
       </c>
       <c r="F24">
-        <v>2563.264</v>
+        <v>2679.776</v>
       </c>
       <c r="G24">
         <v>803</v>
@@ -3249,45 +3249,45 @@
         <v>1700</v>
       </c>
       <c r="M24">
-        <v>128.9321792</v>
+        <v>138.8123968</v>
       </c>
       <c r="N24">
-        <v>1571.0678208</v>
+        <v>1561.1876032</v>
       </c>
       <c r="O24">
-        <v>391.82431450752</v>
+        <v>389.36018823808</v>
       </c>
       <c r="P24">
-        <v>1179.24350629248</v>
+        <v>1171.82741496192</v>
       </c>
       <c r="Q24">
-        <v>2459.24350629248</v>
+        <v>2451.82741496192</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.07918168748552815</v>
+        <v>0.07952598481513137</v>
       </c>
       <c r="T24">
-        <v>0.770939664792798</v>
+        <v>0.7788911042755516</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.2494</v>
       </c>
       <c r="W24">
-        <v>0.03775517999999999</v>
+        <v>0.03888108</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.18522660943281</v>
+        <v>12.24674480946647</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07017765670765116</v>
+        <v>0.07003975957659038</v>
       </c>
       <c r="C25">
-        <v>8638.597047108555</v>
+        <v>8533.558617446892</v>
       </c>
       <c r="D25">
-        <v>10515.37304710855</v>
+        <v>10526.84661744689</v>
       </c>
       <c r="E25">
-        <v>-4682.224</v>
+        <v>-4565.712</v>
       </c>
       <c r="F25">
-        <v>2679.776</v>
+        <v>2796.288</v>
       </c>
       <c r="G25">
         <v>803</v>
@@ -3331,28 +3331,28 @@
         <v>1700</v>
       </c>
       <c r="M25">
-        <v>138.8123968</v>
+        <v>144.8477184</v>
       </c>
       <c r="N25">
-        <v>1561.1876032</v>
+        <v>1555.1522816</v>
       </c>
       <c r="O25">
-        <v>389.36018823808</v>
+        <v>387.85497903104</v>
       </c>
       <c r="P25">
-        <v>1171.82741496192</v>
+        <v>1167.29730256896</v>
       </c>
       <c r="Q25">
-        <v>2451.82741496192</v>
+        <v>2447.29730256896</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.07952598481513137</v>
+        <v>0.07987934260077681</v>
       </c>
       <c r="T25">
-        <v>0.7788911042755516</v>
+        <v>0.7870517921657463</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.24674480946647</v>
+        <v>11.7364637757387</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07003975957659038</v>
+        <v>0.06990186244552958</v>
       </c>
       <c r="C26">
-        <v>8533.558617446892</v>
+        <v>8428.545253298587</v>
       </c>
       <c r="D26">
-        <v>10526.84661744689</v>
+        <v>10538.34525329859</v>
       </c>
       <c r="E26">
-        <v>-4565.712</v>
+        <v>-4449.2</v>
       </c>
       <c r="F26">
-        <v>2796.288</v>
+        <v>2912.8</v>
       </c>
       <c r="G26">
         <v>803</v>
@@ -3413,28 +3413,28 @@
         <v>1700</v>
       </c>
       <c r="M26">
-        <v>144.8477184</v>
+        <v>150.88304</v>
       </c>
       <c r="N26">
-        <v>1555.1522816</v>
+        <v>1549.11696</v>
       </c>
       <c r="O26">
-        <v>387.85497903104</v>
+        <v>386.349769824</v>
       </c>
       <c r="P26">
-        <v>1167.29730256896</v>
+        <v>1162.767190176</v>
       </c>
       <c r="Q26">
-        <v>2447.29730256896</v>
+        <v>2442.767190176</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.07987934260077681</v>
+        <v>0.08024212326070611</v>
       </c>
       <c r="T26">
-        <v>0.7870517921657463</v>
+        <v>0.7954300983996793</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.7364637757387</v>
+        <v>11.26700522470915</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.06990186244552958</v>
+        <v>0.0697639653144688</v>
       </c>
       <c r="C27">
-        <v>8428.545253298587</v>
+        <v>8323.557036891787</v>
       </c>
       <c r="D27">
-        <v>10538.34525329859</v>
+        <v>10549.86903689179</v>
       </c>
       <c r="E27">
-        <v>-4449.2</v>
+        <v>-4332.688</v>
       </c>
       <c r="F27">
-        <v>2912.8</v>
+        <v>3029.312</v>
       </c>
       <c r="G27">
         <v>803</v>
@@ -3495,28 +3495,28 @@
         <v>1700</v>
       </c>
       <c r="M27">
-        <v>150.88304</v>
+        <v>156.9183616</v>
       </c>
       <c r="N27">
-        <v>1549.11696</v>
+        <v>1543.0816384</v>
       </c>
       <c r="O27">
-        <v>386.349769824</v>
+        <v>384.84456061696</v>
       </c>
       <c r="P27">
-        <v>1162.767190176</v>
+        <v>1158.23707778304</v>
       </c>
       <c r="Q27">
-        <v>2442.767190176</v>
+        <v>2438.23707778304</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08024212326070611</v>
+        <v>0.08061470880333621</v>
       </c>
       <c r="T27">
-        <v>0.7954300983996793</v>
+        <v>0.8040348453426376</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.26700522470915</v>
+        <v>10.83365886991264</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0697639653144688</v>
+        <v>0.069626068183408</v>
       </c>
       <c r="C28">
-        <v>8323.557036891787</v>
+        <v>8218.594050814709</v>
       </c>
       <c r="D28">
-        <v>10549.86903689179</v>
+        <v>10561.41805081471</v>
       </c>
       <c r="E28">
-        <v>-4332.688</v>
+        <v>-4216.175999999999</v>
       </c>
       <c r="F28">
-        <v>3029.312</v>
+        <v>3145.824000000001</v>
       </c>
       <c r="G28">
         <v>803</v>
@@ -3577,28 +3577,28 @@
         <v>1700</v>
       </c>
       <c r="M28">
-        <v>156.9183616</v>
+        <v>162.9536832</v>
       </c>
       <c r="N28">
-        <v>1543.0816384</v>
+        <v>1537.0463168</v>
       </c>
       <c r="O28">
-        <v>384.84456061696</v>
+        <v>383.33935140992</v>
       </c>
       <c r="P28">
-        <v>1158.23707778304</v>
+        <v>1153.70696539008</v>
       </c>
       <c r="Q28">
-        <v>2438.23707778304</v>
+        <v>2433.70696539008</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08061470880333621</v>
+        <v>0.08099750216905205</v>
       </c>
       <c r="T28">
-        <v>0.8040348453426376</v>
+        <v>0.8128753387771838</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.83365886991264</v>
+        <v>10.43241224510106</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.069626068183408</v>
+        <v>0.0694881710523472</v>
       </c>
       <c r="C29">
-        <v>8218.594050814709</v>
+        <v>8113.656378017604</v>
       </c>
       <c r="D29">
-        <v>10561.41805081471</v>
+        <v>10572.99237801761</v>
       </c>
       <c r="E29">
-        <v>-4216.175999999999</v>
+        <v>-4099.663999999999</v>
       </c>
       <c r="F29">
-        <v>3145.824000000001</v>
+        <v>3262.336000000001</v>
       </c>
       <c r="G29">
         <v>803</v>
@@ -3659,28 +3659,28 @@
         <v>1700</v>
       </c>
       <c r="M29">
-        <v>162.9536832</v>
+        <v>168.9890048</v>
       </c>
       <c r="N29">
-        <v>1537.0463168</v>
+        <v>1531.0109952</v>
       </c>
       <c r="O29">
-        <v>383.33935140992</v>
+        <v>381.83414220288</v>
       </c>
       <c r="P29">
-        <v>1153.70696539008</v>
+        <v>1149.17685299712</v>
       </c>
       <c r="Q29">
-        <v>2433.70696539008</v>
+        <v>2429.17685299712</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08099750216905205</v>
+        <v>0.08139092868381556</v>
       </c>
       <c r="T29">
-        <v>0.8128753387771838</v>
+        <v>0.8219614014738008</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.43241224510106</v>
+        <v>10.05982609349031</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0694881710523472</v>
+        <v>0.06972031972128642</v>
       </c>
       <c r="C30">
-        <v>8113.656378017604</v>
+        <v>7977.673663233587</v>
       </c>
       <c r="D30">
-        <v>10572.99237801761</v>
+        <v>10553.52166323359</v>
       </c>
       <c r="E30">
-        <v>-4099.663999999999</v>
+        <v>-3983.152</v>
       </c>
       <c r="F30">
-        <v>3262.336000000001</v>
+        <v>3378.848</v>
       </c>
       <c r="G30">
         <v>803</v>
@@ -3741,45 +3741,45 @@
         <v>1700</v>
       </c>
       <c r="M30">
-        <v>168.9890048</v>
+        <v>180.768368</v>
       </c>
       <c r="N30">
-        <v>1531.0109952</v>
+        <v>1519.231632</v>
       </c>
       <c r="O30">
-        <v>381.83414220288</v>
+        <v>378.8963690208</v>
       </c>
       <c r="P30">
-        <v>1149.17685299712</v>
+        <v>1140.3352629792</v>
       </c>
       <c r="Q30">
-        <v>2429.17685299712</v>
+        <v>2420.3352629792</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08139092868381556</v>
+        <v>0.08179543763561467</v>
       </c>
       <c r="T30">
-        <v>0.8219614014738008</v>
+        <v>0.8313034095984915</v>
       </c>
       <c r="U30">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V30">
         <v>0.2494</v>
       </c>
       <c r="W30">
-        <v>0.03888108</v>
+        <v>0.04015709999999999</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y30">
-        <v>10.05982609349031</v>
+        <v>9.404300203672801</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.06972031972128641</v>
+        <v>0.06959518279022561</v>
       </c>
       <c r="C31">
-        <v>7977.673663233589</v>
+        <v>7871.648198155393</v>
       </c>
       <c r="D31">
-        <v>10553.52166323359</v>
+        <v>10564.00819815539</v>
       </c>
       <c r="E31">
-        <v>-3983.152</v>
+        <v>-3866.64</v>
       </c>
       <c r="F31">
-        <v>3378.848</v>
+        <v>3495.36</v>
       </c>
       <c r="G31">
         <v>803</v>
@@ -3823,28 +3823,28 @@
         <v>1700</v>
       </c>
       <c r="M31">
-        <v>180.768368</v>
+        <v>187.00176</v>
       </c>
       <c r="N31">
-        <v>1519.231632</v>
+        <v>1512.99824</v>
       </c>
       <c r="O31">
-        <v>378.8963690208</v>
+        <v>377.341761056</v>
       </c>
       <c r="P31">
-        <v>1140.3352629792</v>
+        <v>1135.656478944</v>
       </c>
       <c r="Q31">
-        <v>2420.3352629792</v>
+        <v>2415.656478944</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08179543763561467</v>
+        <v>0.0822115039860366</v>
       </c>
       <c r="T31">
-        <v>0.8313034095984914</v>
+        <v>0.8409123322410303</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>9.404300203672802</v>
+        <v>9.090823530217042</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.06959518279022561</v>
+        <v>0.06947004585916482</v>
       </c>
       <c r="C32">
-        <v>7871.648198155393</v>
+        <v>7765.643593752199</v>
       </c>
       <c r="D32">
-        <v>10564.00819815539</v>
+        <v>10574.5155937522</v>
       </c>
       <c r="E32">
-        <v>-3866.64</v>
+        <v>-3750.128</v>
       </c>
       <c r="F32">
-        <v>3495.36</v>
+        <v>3611.872</v>
       </c>
       <c r="G32">
         <v>803</v>
@@ -3905,28 +3905,28 @@
         <v>1700</v>
       </c>
       <c r="M32">
-        <v>187.00176</v>
+        <v>193.235152</v>
       </c>
       <c r="N32">
-        <v>1512.99824</v>
+        <v>1506.764848</v>
       </c>
       <c r="O32">
-        <v>377.341761056</v>
+        <v>375.7871530912</v>
       </c>
       <c r="P32">
-        <v>1135.656478944</v>
+        <v>1130.9776949088</v>
       </c>
       <c r="Q32">
-        <v>2415.656478944</v>
+        <v>2410.9776949088</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.0822115039860366</v>
+        <v>0.08263963023067367</v>
       </c>
       <c r="T32">
-        <v>0.8409123322410303</v>
+        <v>0.8507997743804545</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.090823530217042</v>
+        <v>8.797571158274557</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.06947004585916482</v>
+        <v>0.06934490892810403</v>
       </c>
       <c r="C33">
-        <v>7765.643593752199</v>
+        <v>7659.659912332625</v>
       </c>
       <c r="D33">
-        <v>10574.5155937522</v>
+        <v>10585.04391233263</v>
       </c>
       <c r="E33">
-        <v>-3750.128</v>
+        <v>-3633.616</v>
       </c>
       <c r="F33">
-        <v>3611.872</v>
+        <v>3728.384</v>
       </c>
       <c r="G33">
         <v>803</v>
@@ -3987,28 +3987,28 @@
         <v>1700</v>
       </c>
       <c r="M33">
-        <v>193.235152</v>
+        <v>199.468544</v>
       </c>
       <c r="N33">
-        <v>1506.764848</v>
+        <v>1500.531456</v>
       </c>
       <c r="O33">
-        <v>375.7871530912</v>
+        <v>374.2325451264</v>
       </c>
       <c r="P33">
-        <v>1130.9776949088</v>
+        <v>1126.2989108736</v>
       </c>
       <c r="Q33">
-        <v>2410.9776949088</v>
+        <v>2406.2989108736</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08263963023067367</v>
+        <v>0.08308034842368242</v>
       </c>
       <c r="T33">
-        <v>0.8507997743804545</v>
+        <v>0.8609780236416263</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.797571158274557</v>
+        <v>8.522647059578476</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.06934490892810403</v>
+        <v>0.06921977199704324</v>
       </c>
       <c r="C34">
-        <v>7659.659912332625</v>
+        <v>7553.697216453691</v>
       </c>
       <c r="D34">
-        <v>10585.04391233263</v>
+        <v>10595.59321645369</v>
       </c>
       <c r="E34">
-        <v>-3633.616</v>
+        <v>-3517.103999999999</v>
       </c>
       <c r="F34">
-        <v>3728.384</v>
+        <v>3844.896000000001</v>
       </c>
       <c r="G34">
         <v>803</v>
@@ -4069,28 +4069,28 @@
         <v>1700</v>
       </c>
       <c r="M34">
-        <v>199.468544</v>
+        <v>205.701936</v>
       </c>
       <c r="N34">
-        <v>1500.531456</v>
+        <v>1494.298064</v>
       </c>
       <c r="O34">
-        <v>374.2325451264</v>
+        <v>372.6779371616</v>
       </c>
       <c r="P34">
-        <v>1126.2989108736</v>
+        <v>1121.6201268384</v>
       </c>
       <c r="Q34">
-        <v>2406.2989108736</v>
+        <v>2401.6201268384</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08308034842368242</v>
+        <v>0.08353422238364663</v>
       </c>
       <c r="T34">
-        <v>0.8609780236416263</v>
+        <v>0.8714601012389527</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.522647059578476</v>
+        <v>8.264385027470038</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.06921977199704324</v>
+        <v>0.06909463506598246</v>
       </c>
       <c r="C35">
-        <v>7553.697216453691</v>
+        <v>7447.755568922042</v>
       </c>
       <c r="D35">
-        <v>10595.59321645369</v>
+        <v>10606.16356892204</v>
       </c>
       <c r="E35">
-        <v>-3517.103999999999</v>
+        <v>-3400.592</v>
       </c>
       <c r="F35">
-        <v>3844.896000000001</v>
+        <v>3961.408</v>
       </c>
       <c r="G35">
         <v>803</v>
@@ -4151,28 +4151,28 @@
         <v>1700</v>
       </c>
       <c r="M35">
-        <v>205.701936</v>
+        <v>211.935328</v>
       </c>
       <c r="N35">
-        <v>1494.298064</v>
+        <v>1488.064672</v>
       </c>
       <c r="O35">
-        <v>372.6779371616</v>
+        <v>371.1233291968</v>
       </c>
       <c r="P35">
-        <v>1121.6201268384</v>
+        <v>1116.9413428032</v>
       </c>
       <c r="Q35">
-        <v>2401.6201268384</v>
+        <v>2396.9413428032</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08353422238364663</v>
+        <v>0.08400185009997342</v>
       </c>
       <c r="T35">
-        <v>0.8714601012389527</v>
+        <v>0.8822598175513494</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.264385027470038</v>
+        <v>8.02131487960327</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.06909463506598246</v>
+        <v>0.06896949813492166</v>
       </c>
       <c r="C36">
-        <v>7447.755568922042</v>
+        <v>7341.835032795205</v>
       </c>
       <c r="D36">
-        <v>10606.16356892204</v>
+        <v>10616.7550327952</v>
       </c>
       <c r="E36">
-        <v>-3400.592</v>
+        <v>-3284.079999999999</v>
       </c>
       <c r="F36">
-        <v>3961.408</v>
+        <v>4077.920000000001</v>
       </c>
       <c r="G36">
         <v>803</v>
@@ -4233,28 +4233,28 @@
         <v>1700</v>
       </c>
       <c r="M36">
-        <v>211.935328</v>
+        <v>218.16872</v>
       </c>
       <c r="N36">
-        <v>1488.064672</v>
+        <v>1481.83128</v>
       </c>
       <c r="O36">
-        <v>371.1233291968</v>
+        <v>369.568721232</v>
       </c>
       <c r="P36">
-        <v>1116.9413428032</v>
+        <v>1112.262558768</v>
       </c>
       <c r="Q36">
-        <v>2396.9413428032</v>
+        <v>2392.262558768</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08400185009997342</v>
+        <v>0.08448386636141796</v>
       </c>
       <c r="T36">
-        <v>0.8822598175513494</v>
+        <v>0.8933918328272047</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.02131487960327</v>
+        <v>7.792134454471748</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.06896949813492166</v>
+        <v>0.06906053400386086</v>
       </c>
       <c r="C37">
-        <v>7341.835032795205</v>
+        <v>7217.615753184196</v>
       </c>
       <c r="D37">
-        <v>10616.7550327952</v>
+        <v>10609.0477531842</v>
       </c>
       <c r="E37">
-        <v>-3284.079999999999</v>
+        <v>-3167.567999999999</v>
       </c>
       <c r="F37">
-        <v>4077.920000000001</v>
+        <v>4194.432000000001</v>
       </c>
       <c r="G37">
         <v>803</v>
@@ -4315,45 +4315,45 @@
         <v>1700</v>
       </c>
       <c r="M37">
-        <v>218.16872</v>
+        <v>227.7576576</v>
       </c>
       <c r="N37">
-        <v>1481.83128</v>
+        <v>1472.2423424</v>
       </c>
       <c r="O37">
-        <v>369.568721232</v>
+        <v>367.17724019456</v>
       </c>
       <c r="P37">
-        <v>1112.262558768</v>
+        <v>1105.06510220544</v>
       </c>
       <c r="Q37">
-        <v>2392.262558768</v>
+        <v>2385.06510220544</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08448386636141796</v>
+        <v>0.08498094563103262</v>
       </c>
       <c r="T37">
-        <v>0.8933918328272047</v>
+        <v>0.9048717235804303</v>
       </c>
       <c r="U37">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V37">
         <v>0.2494</v>
       </c>
       <c r="W37">
-        <v>0.04015709999999999</v>
+        <v>0.04075757999999999</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y37">
-        <v>7.792134454471748</v>
+        <v>7.464073954367889</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.06906053400386088</v>
+        <v>0.0689414018728001</v>
       </c>
       <c r="C38">
-        <v>7217.615753184195</v>
+        <v>7111.191980720322</v>
       </c>
       <c r="D38">
-        <v>10609.0477531842</v>
+        <v>10619.13598072032</v>
       </c>
       <c r="E38">
-        <v>-3167.568</v>
+        <v>-3051.056</v>
       </c>
       <c r="F38">
-        <v>4194.432</v>
+        <v>4310.944</v>
       </c>
       <c r="G38">
         <v>803</v>
@@ -4397,28 +4397,28 @@
         <v>1700</v>
       </c>
       <c r="M38">
-        <v>227.7576576</v>
+        <v>234.0842592</v>
       </c>
       <c r="N38">
-        <v>1472.2423424</v>
+        <v>1465.9157408</v>
       </c>
       <c r="O38">
-        <v>367.1772401945601</v>
+        <v>365.59938575552</v>
       </c>
       <c r="P38">
-        <v>1105.06510220544</v>
+        <v>1100.31635504448</v>
       </c>
       <c r="Q38">
-        <v>2385.06510220544</v>
+        <v>2380.31635504448</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08498094563103262</v>
+        <v>0.08549380519492078</v>
       </c>
       <c r="T38">
-        <v>0.9048717235804303</v>
+        <v>0.9167160553099487</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.464073954367891</v>
+        <v>7.26234222587146</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0689414018728001</v>
+        <v>0.06882226974173929</v>
       </c>
       <c r="C39">
-        <v>7111.191980720322</v>
+        <v>7004.787412468824</v>
       </c>
       <c r="D39">
-        <v>10619.13598072032</v>
+        <v>10629.24341246882</v>
       </c>
       <c r="E39">
-        <v>-3051.056</v>
+        <v>-2934.544</v>
       </c>
       <c r="F39">
-        <v>4310.944</v>
+        <v>4427.456</v>
       </c>
       <c r="G39">
         <v>803</v>
@@ -4479,28 +4479,28 @@
         <v>1700</v>
       </c>
       <c r="M39">
-        <v>234.0842592</v>
+        <v>240.4108608</v>
       </c>
       <c r="N39">
-        <v>1465.9157408</v>
+        <v>1459.5891392</v>
       </c>
       <c r="O39">
-        <v>365.59938575552</v>
+        <v>364.02153131648</v>
       </c>
       <c r="P39">
-        <v>1100.31635504448</v>
+        <v>1095.56760788352</v>
       </c>
       <c r="Q39">
-        <v>2380.31635504448</v>
+        <v>2375.56760788352</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08549380519492078</v>
+        <v>0.08602320861570853</v>
       </c>
       <c r="T39">
-        <v>0.9167160553099487</v>
+        <v>0.9289424622565484</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.26234222587146</v>
+        <v>7.071227956769579</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.06882226974173929</v>
+        <v>0.06870313761067851</v>
       </c>
       <c r="C40">
-        <v>7004.787412468824</v>
+        <v>6898.402103318394</v>
       </c>
       <c r="D40">
-        <v>10629.24341246882</v>
+        <v>10639.3701033184</v>
       </c>
       <c r="E40">
-        <v>-2934.544</v>
+        <v>-2818.031999999999</v>
       </c>
       <c r="F40">
-        <v>4427.456</v>
+        <v>4543.968000000001</v>
       </c>
       <c r="G40">
         <v>803</v>
@@ -4561,28 +4561,28 @@
         <v>1700</v>
       </c>
       <c r="M40">
-        <v>240.4108608</v>
+        <v>246.7374624000001</v>
       </c>
       <c r="N40">
-        <v>1459.5891392</v>
+        <v>1453.2625376</v>
       </c>
       <c r="O40">
-        <v>364.02153131648</v>
+        <v>362.44367687744</v>
       </c>
       <c r="P40">
-        <v>1095.56760788352</v>
+        <v>1090.81886072256</v>
       </c>
       <c r="Q40">
-        <v>2375.56760788352</v>
+        <v>2370.81886072256</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.08602320861570853</v>
+        <v>0.08656996952570248</v>
       </c>
       <c r="T40">
-        <v>0.9289424622565484</v>
+        <v>0.9415697350046761</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.071227956769579</v>
+        <v>6.889914419416512</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.06870313761067851</v>
+        <v>0.06858400547961771</v>
       </c>
       <c r="C41">
-        <v>6898.402103318394</v>
+        <v>6792.036108367113</v>
       </c>
       <c r="D41">
-        <v>10639.3701033184</v>
+        <v>10649.51610836711</v>
       </c>
       <c r="E41">
-        <v>-2818.031999999999</v>
+        <v>-2701.52</v>
       </c>
       <c r="F41">
-        <v>4543.968000000001</v>
+        <v>4660.48</v>
       </c>
       <c r="G41">
         <v>803</v>
@@ -4643,28 +4643,28 @@
         <v>1700</v>
       </c>
       <c r="M41">
-        <v>246.7374624000001</v>
+        <v>253.064064</v>
       </c>
       <c r="N41">
-        <v>1453.2625376</v>
+        <v>1446.935936</v>
       </c>
       <c r="O41">
-        <v>362.44367687744</v>
+        <v>360.8658224384</v>
       </c>
       <c r="P41">
-        <v>1090.81886072256</v>
+        <v>1086.0701135616</v>
       </c>
       <c r="Q41">
-        <v>2370.81886072256</v>
+        <v>2366.0701135616</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.08656996952570248</v>
+        <v>0.08713495579936285</v>
       </c>
       <c r="T41">
-        <v>0.9415697350046761</v>
+        <v>0.9546179168444079</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.889914419416512</v>
+        <v>6.7176665589311</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.06858400547961771</v>
+        <v>0.06846487334855691</v>
       </c>
       <c r="C42">
-        <v>6792.036108367113</v>
+        <v>6685.689482923427</v>
       </c>
       <c r="D42">
-        <v>10649.51610836711</v>
+        <v>10659.68148292343</v>
       </c>
       <c r="E42">
-        <v>-2701.52</v>
+        <v>-2585.007999999999</v>
       </c>
       <c r="F42">
-        <v>4660.48</v>
+        <v>4776.992000000001</v>
       </c>
       <c r="G42">
         <v>803</v>
@@ -4725,28 +4725,28 @@
         <v>1700</v>
       </c>
       <c r="M42">
-        <v>253.064064</v>
+        <v>259.3906656000001</v>
       </c>
       <c r="N42">
-        <v>1446.935936</v>
+        <v>1440.6093344</v>
       </c>
       <c r="O42">
-        <v>360.8658224384</v>
+        <v>359.28796799936</v>
       </c>
       <c r="P42">
-        <v>1086.0701135616</v>
+        <v>1081.32136640064</v>
       </c>
       <c r="Q42">
-        <v>2366.0701135616</v>
+        <v>2361.32136640064</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.08713495579936285</v>
+        <v>0.08771909415009649</v>
       </c>
       <c r="T42">
-        <v>0.9546179168444079</v>
+        <v>0.9681084099329443</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.7176665589311</v>
+        <v>6.553821033103511</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.06846487334855691</v>
+        <v>0.06834574121749613</v>
       </c>
       <c r="C43">
-        <v>6685.689482923427</v>
+        <v>6579.36228250716</v>
       </c>
       <c r="D43">
-        <v>10659.68148292343</v>
+        <v>10669.86628250716</v>
       </c>
       <c r="E43">
-        <v>-2585.007999999999</v>
+        <v>-2468.495999999999</v>
       </c>
       <c r="F43">
-        <v>4776.992000000001</v>
+        <v>4893.504000000001</v>
       </c>
       <c r="G43">
         <v>803</v>
@@ -4807,28 +4807,28 @@
         <v>1700</v>
       </c>
       <c r="M43">
-        <v>259.3906656000001</v>
+        <v>265.7172672</v>
       </c>
       <c r="N43">
-        <v>1440.6093344</v>
+        <v>1434.2827328</v>
       </c>
       <c r="O43">
-        <v>359.28796799936</v>
+        <v>357.71011356032</v>
       </c>
       <c r="P43">
-        <v>1081.32136640064</v>
+        <v>1076.57261923968</v>
       </c>
       <c r="Q43">
-        <v>2361.32136640064</v>
+        <v>2356.57261923968</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.08771909415009649</v>
+        <v>0.08832337520257955</v>
       </c>
       <c r="T43">
-        <v>0.9681084099329443</v>
+        <v>0.9820640924383267</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.553821033103511</v>
+        <v>6.397777675172476</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.06834574121749613</v>
+        <v>0.06822660908643534</v>
       </c>
       <c r="C44">
-        <v>6579.362282507161</v>
+        <v>6473.054562850531</v>
       </c>
       <c r="D44">
-        <v>10669.86628250716</v>
+        <v>10680.07056285053</v>
       </c>
       <c r="E44">
-        <v>-2468.496</v>
+        <v>-2351.983999999999</v>
       </c>
       <c r="F44">
-        <v>4893.504</v>
+        <v>5010.016000000001</v>
       </c>
       <c r="G44">
         <v>803</v>
@@ -4889,28 +4889,28 @@
         <v>1700</v>
       </c>
       <c r="M44">
-        <v>265.7172672</v>
+        <v>272.0438688</v>
       </c>
       <c r="N44">
-        <v>1434.2827328</v>
+        <v>1427.9561312</v>
       </c>
       <c r="O44">
-        <v>357.7101135603201</v>
+        <v>356.13225912128</v>
       </c>
       <c r="P44">
-        <v>1076.57261923968</v>
+        <v>1071.82387207872</v>
       </c>
       <c r="Q44">
-        <v>2356.57261923968</v>
+        <v>2351.82387207872</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.08832337520257953</v>
+        <v>0.08894885909900936</v>
       </c>
       <c r="T44">
-        <v>0.9820640924383266</v>
+        <v>0.9965094480140733</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.397777675172478</v>
+        <v>6.248992147842884</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.06822660908643534</v>
+        <v>0.06843774095537455</v>
       </c>
       <c r="C45">
-        <v>6473.054562850531</v>
+        <v>6338.471365090776</v>
       </c>
       <c r="D45">
-        <v>10680.07056285053</v>
+        <v>10661.99936509078</v>
       </c>
       <c r="E45">
-        <v>-2351.983999999999</v>
+        <v>-2235.472</v>
       </c>
       <c r="F45">
-        <v>5010.016000000001</v>
+        <v>5126.528</v>
       </c>
       <c r="G45">
         <v>803</v>
@@ -4971,45 +4971,45 @@
         <v>1700</v>
       </c>
       <c r="M45">
-        <v>272.0438688</v>
+        <v>283.4969984</v>
       </c>
       <c r="N45">
-        <v>1427.9561312</v>
+        <v>1416.5030016</v>
       </c>
       <c r="O45">
-        <v>356.13225912128</v>
+        <v>353.27584859904</v>
       </c>
       <c r="P45">
-        <v>1071.82387207872</v>
+        <v>1063.22715300096</v>
       </c>
       <c r="Q45">
-        <v>2351.82387207872</v>
+        <v>2343.22715300096</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.08894885909900936</v>
+        <v>0.08959668170602597</v>
       </c>
       <c r="T45">
-        <v>0.9965094480140733</v>
+        <v>1.011470709146097</v>
       </c>
       <c r="U45">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V45">
         <v>0.2494</v>
       </c>
       <c r="W45">
-        <v>0.04075757999999999</v>
+        <v>0.04150818</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y45">
-        <v>6.248992147842884</v>
+        <v>5.996536152391235</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.06843774095537455</v>
+        <v>0.06832611482431376</v>
       </c>
       <c r="C46">
-        <v>6338.471365090776</v>
+        <v>6231.50604231792</v>
       </c>
       <c r="D46">
-        <v>10661.99936509078</v>
+        <v>10671.54604231792</v>
       </c>
       <c r="E46">
-        <v>-2235.472</v>
+        <v>-2118.959999999999</v>
       </c>
       <c r="F46">
-        <v>5126.528</v>
+        <v>5243.040000000001</v>
       </c>
       <c r="G46">
         <v>803</v>
@@ -5053,28 +5053,28 @@
         <v>1700</v>
       </c>
       <c r="M46">
-        <v>283.4969984</v>
+        <v>289.9401120000001</v>
       </c>
       <c r="N46">
-        <v>1416.5030016</v>
+        <v>1410.059888</v>
       </c>
       <c r="O46">
-        <v>353.27584859904</v>
+        <v>351.6689360672</v>
       </c>
       <c r="P46">
-        <v>1063.22715300096</v>
+        <v>1058.3909519328</v>
       </c>
       <c r="Q46">
-        <v>2343.22715300096</v>
+        <v>2338.3909519328</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.08959668170602597</v>
+        <v>0.09026806149875229</v>
       </c>
       <c r="T46">
-        <v>1.011470709146097</v>
+        <v>1.026976016137466</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.996536152391235</v>
+        <v>5.863279793449206</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.06832611482431376</v>
+        <v>0.06821448869325297</v>
       </c>
       <c r="C47">
-        <v>6231.50604231792</v>
+        <v>6124.557830918145</v>
       </c>
       <c r="D47">
-        <v>10671.54604231792</v>
+        <v>10681.10983091815</v>
       </c>
       <c r="E47">
-        <v>-2118.959999999999</v>
+        <v>-2002.447999999999</v>
       </c>
       <c r="F47">
-        <v>5243.040000000001</v>
+        <v>5359.552000000001</v>
       </c>
       <c r="G47">
         <v>803</v>
@@ -5135,28 +5135,28 @@
         <v>1700</v>
       </c>
       <c r="M47">
-        <v>289.9401120000001</v>
+        <v>296.3832256000001</v>
       </c>
       <c r="N47">
-        <v>1410.059888</v>
+        <v>1403.6167744</v>
       </c>
       <c r="O47">
-        <v>351.6689360672</v>
+        <v>350.06202353536</v>
       </c>
       <c r="P47">
-        <v>1058.3909519328</v>
+        <v>1053.55475086464</v>
       </c>
       <c r="Q47">
-        <v>2338.3909519328</v>
+        <v>2333.55475086464</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09026806149875229</v>
+        <v>0.09096430720972772</v>
       </c>
       <c r="T47">
-        <v>1.026976016137466</v>
+        <v>1.043055593758146</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.863279793449206</v>
+        <v>5.735817189243789</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.06821448869325297</v>
+        <v>0.06810286256219218</v>
       </c>
       <c r="C48">
-        <v>6124.557830918145</v>
+        <v>6017.626776938107</v>
       </c>
       <c r="D48">
-        <v>10681.10983091815</v>
+        <v>10690.69077693811</v>
       </c>
       <c r="E48">
-        <v>-2002.447999999999</v>
+        <v>-1885.936</v>
       </c>
       <c r="F48">
-        <v>5359.552000000001</v>
+        <v>5476.064</v>
       </c>
       <c r="G48">
         <v>803</v>
@@ -5217,28 +5217,28 @@
         <v>1700</v>
       </c>
       <c r="M48">
-        <v>296.3832256000001</v>
+        <v>302.8263392</v>
       </c>
       <c r="N48">
-        <v>1403.6167744</v>
+        <v>1397.1736608</v>
       </c>
       <c r="O48">
-        <v>350.06202353536</v>
+        <v>348.45511100352</v>
       </c>
       <c r="P48">
-        <v>1053.55475086464</v>
+        <v>1048.71854979648</v>
       </c>
       <c r="Q48">
-        <v>2333.55475086464</v>
+        <v>2328.71854979648</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09096430720972772</v>
+        <v>0.09168682634375883</v>
       </c>
       <c r="T48">
-        <v>1.043055593758146</v>
+        <v>1.059741947892814</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.735817189243789</v>
+        <v>5.613778525642858</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06810286256219218</v>
+        <v>0.06799123643113139</v>
       </c>
       <c r="C49">
-        <v>6017.626776938107</v>
+        <v>5910.712926589829</v>
       </c>
       <c r="D49">
-        <v>10690.69077693811</v>
+        <v>10700.28892658983</v>
       </c>
       <c r="E49">
-        <v>-1885.936</v>
+        <v>-1769.423999999999</v>
       </c>
       <c r="F49">
-        <v>5476.064</v>
+        <v>5592.576000000001</v>
       </c>
       <c r="G49">
         <v>803</v>
@@ -5299,28 +5299,28 @@
         <v>1700</v>
       </c>
       <c r="M49">
-        <v>302.8263392</v>
+        <v>309.2694528000001</v>
       </c>
       <c r="N49">
-        <v>1397.1736608</v>
+        <v>1390.7305472</v>
       </c>
       <c r="O49">
-        <v>348.45511100352</v>
+        <v>346.84819847168</v>
       </c>
       <c r="P49">
-        <v>1048.71854979648</v>
+        <v>1043.88234872832</v>
       </c>
       <c r="Q49">
-        <v>2328.71854979648</v>
+        <v>2323.88234872832</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09168682634375883</v>
+        <v>0.09243713467525266</v>
       </c>
       <c r="T49">
-        <v>1.059741947892814</v>
+        <v>1.077070084878815</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.613778525642858</v>
+        <v>5.49682480635863</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06799123643113139</v>
+        <v>0.0678796103000706</v>
       </c>
       <c r="C50">
-        <v>5910.71292658983</v>
+        <v>5803.816326251447</v>
       </c>
       <c r="D50">
-        <v>10700.28892658983</v>
+        <v>10709.90432625145</v>
       </c>
       <c r="E50">
-        <v>-1769.424</v>
+        <v>-1652.911999999999</v>
       </c>
       <c r="F50">
-        <v>5592.576</v>
+        <v>5709.088000000001</v>
       </c>
       <c r="G50">
         <v>803</v>
@@ -5381,28 +5381,28 @@
         <v>1700</v>
       </c>
       <c r="M50">
-        <v>309.2694528</v>
+        <v>315.7125664000001</v>
       </c>
       <c r="N50">
-        <v>1390.7305472</v>
+        <v>1384.2874336</v>
       </c>
       <c r="O50">
-        <v>346.84819847168</v>
+        <v>345.24128593984</v>
       </c>
       <c r="P50">
-        <v>1043.88234872832</v>
+        <v>1039.04614766016</v>
       </c>
       <c r="Q50">
-        <v>2323.88234872832</v>
+        <v>2319.04614766016</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09243713467525266</v>
+        <v>0.09321686686288352</v>
       </c>
       <c r="T50">
-        <v>1.077070084878814</v>
+        <v>1.09507775664858</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.496824806358632</v>
+        <v>5.384644708269679</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.0678796103000706</v>
+        <v>0.06776798416900981</v>
       </c>
       <c r="C51">
-        <v>5803.816326251447</v>
+        <v>5696.937022467939</v>
       </c>
       <c r="D51">
-        <v>10709.90432625145</v>
+        <v>10719.53702246794</v>
       </c>
       <c r="E51">
-        <v>-1652.911999999999</v>
+        <v>-1536.4</v>
       </c>
       <c r="F51">
-        <v>5709.088000000001</v>
+        <v>5825.6</v>
       </c>
       <c r="G51">
         <v>803</v>
@@ -5463,28 +5463,28 @@
         <v>1700</v>
       </c>
       <c r="M51">
-        <v>315.7125664000001</v>
+        <v>322.15568</v>
       </c>
       <c r="N51">
-        <v>1384.2874336</v>
+        <v>1377.84432</v>
       </c>
       <c r="O51">
-        <v>345.24128593984</v>
+        <v>343.634373408</v>
       </c>
       <c r="P51">
-        <v>1039.04614766016</v>
+        <v>1034.209946592</v>
       </c>
       <c r="Q51">
-        <v>2319.04614766016</v>
+        <v>2314.209946592</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09321686686288352</v>
+        <v>0.09402778833801961</v>
       </c>
       <c r="T51">
-        <v>1.09507775664858</v>
+        <v>1.113805735289137</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.384644708269679</v>
+        <v>5.276951814104286</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06776798416900981</v>
+        <v>0.06765635803794902</v>
       </c>
       <c r="C52">
-        <v>5696.937022467939</v>
+        <v>5590.075061951892</v>
       </c>
       <c r="D52">
-        <v>10719.53702246794</v>
+        <v>10729.18706195189</v>
       </c>
       <c r="E52">
-        <v>-1536.4</v>
+        <v>-1419.888</v>
       </c>
       <c r="F52">
-        <v>5825.6</v>
+        <v>5942.112</v>
       </c>
       <c r="G52">
         <v>803</v>
@@ -5545,28 +5545,28 @@
         <v>1700</v>
       </c>
       <c r="M52">
-        <v>322.15568</v>
+        <v>328.5987936</v>
       </c>
       <c r="N52">
-        <v>1377.84432</v>
+        <v>1371.4012064</v>
       </c>
       <c r="O52">
-        <v>343.634373408</v>
+        <v>342.02746087616</v>
       </c>
       <c r="P52">
-        <v>1034.209946592</v>
+        <v>1029.37374552384</v>
       </c>
       <c r="Q52">
-        <v>2314.209946592</v>
+        <v>2309.37374552384</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09402778833801961</v>
+        <v>0.09487180864887554</v>
       </c>
       <c r="T52">
-        <v>1.113805735289137</v>
+        <v>1.133298121221144</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.276951814104286</v>
+        <v>5.173482170690476</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06765635803794902</v>
+        <v>0.06754473190688823</v>
       </c>
       <c r="C53">
-        <v>5590.075061951892</v>
+        <v>5483.230491584253</v>
       </c>
       <c r="D53">
-        <v>10729.18706195189</v>
+        <v>10738.85449158425</v>
       </c>
       <c r="E53">
-        <v>-1419.888</v>
+        <v>-1303.375999999999</v>
       </c>
       <c r="F53">
-        <v>5942.112</v>
+        <v>6058.624000000001</v>
       </c>
       <c r="G53">
         <v>803</v>
@@ -5627,28 +5627,28 @@
         <v>1700</v>
       </c>
       <c r="M53">
-        <v>328.5987936</v>
+        <v>335.0419072</v>
       </c>
       <c r="N53">
-        <v>1371.4012064</v>
+        <v>1364.9580928</v>
       </c>
       <c r="O53">
-        <v>342.02746087616</v>
+        <v>340.42054834432</v>
       </c>
       <c r="P53">
-        <v>1029.37374552384</v>
+        <v>1024.53754445568</v>
       </c>
       <c r="Q53">
-        <v>2309.37374552384</v>
+        <v>2304.53754445568</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.09487180864887554</v>
+        <v>0.0957509964726838</v>
       </c>
       <c r="T53">
-        <v>1.133298121221144</v>
+        <v>1.153602689900319</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.173482170690476</v>
+        <v>5.073992128946429</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06754473190688823</v>
+        <v>0.06743310577582742</v>
       </c>
       <c r="C54">
-        <v>5483.230491584253</v>
+        <v>5376.403358415095</v>
       </c>
       <c r="D54">
-        <v>10738.85449158425</v>
+        <v>10748.5393584151</v>
       </c>
       <c r="E54">
-        <v>-1303.375999999999</v>
+        <v>-1186.864</v>
       </c>
       <c r="F54">
-        <v>6058.624000000001</v>
+        <v>6175.136</v>
       </c>
       <c r="G54">
         <v>803</v>
@@ -5709,28 +5709,28 @@
         <v>1700</v>
       </c>
       <c r="M54">
-        <v>335.0419072</v>
+        <v>341.4850208</v>
       </c>
       <c r="N54">
-        <v>1364.9580928</v>
+        <v>1358.5149792</v>
       </c>
       <c r="O54">
-        <v>340.42054834432</v>
+        <v>338.81363581248</v>
       </c>
       <c r="P54">
-        <v>1024.53754445568</v>
+        <v>1019.70134338752</v>
       </c>
       <c r="Q54">
-        <v>2304.53754445568</v>
+        <v>2299.70134338752</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.0957509964726838</v>
+        <v>0.09666759654431367</v>
       </c>
       <c r="T54">
-        <v>1.153602689900319</v>
+        <v>1.174771282778607</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.073992128946429</v>
+        <v>4.97825642840027</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06743310577582742</v>
+        <v>0.06732147964476665</v>
       </c>
       <c r="C55">
-        <v>5376.403358415095</v>
+        <v>5269.593709664356</v>
       </c>
       <c r="D55">
-        <v>10748.5393584151</v>
+        <v>10758.24170966436</v>
       </c>
       <c r="E55">
-        <v>-1186.864</v>
+        <v>-1070.351999999999</v>
       </c>
       <c r="F55">
-        <v>6175.136</v>
+        <v>6291.648000000001</v>
       </c>
       <c r="G55">
         <v>803</v>
@@ -5791,28 +5791,28 @@
         <v>1700</v>
       </c>
       <c r="M55">
-        <v>341.4850208</v>
+        <v>347.9281344000001</v>
       </c>
       <c r="N55">
-        <v>1358.5149792</v>
+        <v>1352.0718656</v>
       </c>
       <c r="O55">
-        <v>338.81363581248</v>
+        <v>337.20672328064</v>
       </c>
       <c r="P55">
-        <v>1019.70134338752</v>
+        <v>1014.86514231936</v>
       </c>
       <c r="Q55">
-        <v>2299.70134338752</v>
+        <v>2294.86514231936</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.09666759654431367</v>
+        <v>0.09762404879297096</v>
       </c>
       <c r="T55">
-        <v>1.174771282778607</v>
+        <v>1.196860249260299</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.97825642840027</v>
+        <v>4.886066494541005</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06732147964476665</v>
+        <v>0.06720985351370586</v>
       </c>
       <c r="C56">
-        <v>5269.593709664356</v>
+        <v>5162.80159272264</v>
       </c>
       <c r="D56">
-        <v>10758.24170966436</v>
+        <v>10767.96159272264</v>
       </c>
       <c r="E56">
-        <v>-1070.351999999999</v>
+        <v>-953.8399999999992</v>
       </c>
       <c r="F56">
-        <v>6291.648000000001</v>
+        <v>6408.160000000001</v>
       </c>
       <c r="G56">
         <v>803</v>
@@ -5873,28 +5873,28 @@
         <v>1700</v>
       </c>
       <c r="M56">
-        <v>347.9281344000001</v>
+        <v>354.371248</v>
       </c>
       <c r="N56">
-        <v>1352.0718656</v>
+        <v>1345.628752</v>
       </c>
       <c r="O56">
-        <v>337.20672328064</v>
+        <v>335.5998107488001</v>
       </c>
       <c r="P56">
-        <v>1014.86514231936</v>
+        <v>1010.0289412512</v>
       </c>
       <c r="Q56">
-        <v>2294.86514231936</v>
+        <v>2290.0289412512</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.09762404879297096</v>
+        <v>0.09862301003045745</v>
       </c>
       <c r="T56">
-        <v>1.196860249260299</v>
+        <v>1.219930947585623</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.886066494541005</v>
+        <v>4.797228921912987</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06720985351370586</v>
+        <v>0.06709822738264505</v>
       </c>
       <c r="C57">
-        <v>5162.80159272264</v>
+        <v>5056.027055151965</v>
       </c>
       <c r="D57">
-        <v>10767.96159272264</v>
+        <v>10777.69905515197</v>
       </c>
       <c r="E57">
-        <v>-953.8399999999992</v>
+        <v>-837.3279999999986</v>
       </c>
       <c r="F57">
-        <v>6408.160000000001</v>
+        <v>6524.672000000001</v>
       </c>
       <c r="G57">
         <v>803</v>
@@ -5955,28 +5955,28 @@
         <v>1700</v>
       </c>
       <c r="M57">
-        <v>354.371248</v>
+        <v>360.8143616000001</v>
       </c>
       <c r="N57">
-        <v>1345.628752</v>
+        <v>1339.1856384</v>
       </c>
       <c r="O57">
-        <v>335.5998107488001</v>
+        <v>333.99289821696</v>
       </c>
       <c r="P57">
-        <v>1010.0289412512</v>
+        <v>1005.19274018304</v>
       </c>
       <c r="Q57">
-        <v>2290.0289412512</v>
+        <v>2285.19274018304</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.09862301003045745</v>
+        <v>0.09966737859692058</v>
       </c>
       <c r="T57">
-        <v>1.219930947585623</v>
+        <v>1.244050314016642</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.797228921912987</v>
+        <v>4.711564119735968</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06709822738264505</v>
+        <v>0.06698660125158426</v>
       </c>
       <c r="C58">
-        <v>5056.027055151965</v>
+        <v>4949.27014468655</v>
       </c>
       <c r="D58">
-        <v>10777.69905515197</v>
+        <v>10787.45414468655</v>
       </c>
       <c r="E58">
-        <v>-837.3279999999986</v>
+        <v>-720.8159999999989</v>
       </c>
       <c r="F58">
-        <v>6524.672000000001</v>
+        <v>6641.184000000001</v>
       </c>
       <c r="G58">
         <v>803</v>
@@ -6037,28 +6037,28 @@
         <v>1700</v>
       </c>
       <c r="M58">
-        <v>360.8143616000001</v>
+        <v>367.2574752000001</v>
       </c>
       <c r="N58">
-        <v>1339.1856384</v>
+        <v>1332.7425248</v>
       </c>
       <c r="O58">
-        <v>333.99289821696</v>
+        <v>332.38598568512</v>
       </c>
       <c r="P58">
-        <v>1005.19274018304</v>
+        <v>1000.35653911488</v>
       </c>
       <c r="Q58">
-        <v>2285.19274018304</v>
+        <v>2280.35653911488</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.09966737859692058</v>
+        <v>0.1007603224455448</v>
       </c>
       <c r="T58">
-        <v>1.244050314016642</v>
+        <v>1.269291511444453</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.711564119735968</v>
+        <v>4.628905100091478</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06698660125158426</v>
+        <v>0.06687497512052347</v>
       </c>
       <c r="C59">
-        <v>4949.27014468655</v>
+        <v>4842.530909233582</v>
       </c>
       <c r="D59">
-        <v>10787.45414468655</v>
+        <v>10797.22690923358</v>
       </c>
       <c r="E59">
-        <v>-720.8159999999989</v>
+        <v>-604.3039999999992</v>
       </c>
       <c r="F59">
-        <v>6641.184000000001</v>
+        <v>6757.696000000001</v>
       </c>
       <c r="G59">
         <v>803</v>
@@ -6119,28 +6119,28 @@
         <v>1700</v>
       </c>
       <c r="M59">
-        <v>367.2574752000001</v>
+        <v>373.7005888</v>
       </c>
       <c r="N59">
-        <v>1332.7425248</v>
+        <v>1326.2994112</v>
       </c>
       <c r="O59">
-        <v>332.38598568512</v>
+        <v>330.77907315328</v>
       </c>
       <c r="P59">
-        <v>1000.35653911488</v>
+        <v>995.5203380467199</v>
       </c>
       <c r="Q59">
-        <v>2280.35653911488</v>
+        <v>2275.52033804672</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1007603224455448</v>
+        <v>0.1019053112393416</v>
       </c>
       <c r="T59">
-        <v>1.269291511444453</v>
+        <v>1.295734670654541</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.628905100091478</v>
+        <v>4.549096391469211</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06687497512052347</v>
+        <v>0.06787048398946269</v>
       </c>
       <c r="C60">
-        <v>4842.530909233583</v>
+        <v>4639.483224734774</v>
       </c>
       <c r="D60">
-        <v>10797.22690923358</v>
+        <v>10710.69122473477</v>
       </c>
       <c r="E60">
-        <v>-604.3040000000001</v>
+        <v>-487.7920000000004</v>
       </c>
       <c r="F60">
-        <v>6757.696</v>
+        <v>6874.208</v>
       </c>
       <c r="G60">
         <v>803</v>
@@ -6201,45 +6201,45 @@
         <v>1700</v>
       </c>
       <c r="M60">
-        <v>373.7005888</v>
+        <v>397.3292224</v>
       </c>
       <c r="N60">
-        <v>1326.2994112</v>
+        <v>1302.6707776</v>
       </c>
       <c r="O60">
-        <v>330.77907315328</v>
+        <v>324.88609193344</v>
       </c>
       <c r="P60">
-        <v>995.5203380467201</v>
+        <v>977.7846856665601</v>
       </c>
       <c r="Q60">
-        <v>2275.52033804672</v>
+        <v>2257.78468566656</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1019053112393416</v>
+        <v>0.1031061531450309</v>
       </c>
       <c r="T60">
-        <v>1.295734670654541</v>
+        <v>1.323467740069999</v>
       </c>
       <c r="U60">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V60">
         <v>0.2494</v>
       </c>
       <c r="W60">
-        <v>0.04150818</v>
+        <v>0.04338468</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y60">
-        <v>4.549096391469213</v>
+        <v>4.278567757315804</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06787048398946269</v>
+        <v>0.06777762285840189</v>
       </c>
       <c r="C61">
-        <v>4639.483224734774</v>
+        <v>4530.984575286512</v>
       </c>
       <c r="D61">
-        <v>10710.69122473477</v>
+        <v>10718.70457528651</v>
       </c>
       <c r="E61">
-        <v>-487.7920000000004</v>
+        <v>-371.2799999999997</v>
       </c>
       <c r="F61">
-        <v>6874.208</v>
+        <v>6990.72</v>
       </c>
       <c r="G61">
         <v>803</v>
@@ -6283,28 +6283,28 @@
         <v>1700</v>
       </c>
       <c r="M61">
-        <v>397.3292224</v>
+        <v>404.063616</v>
       </c>
       <c r="N61">
-        <v>1302.6707776</v>
+        <v>1295.936384</v>
       </c>
       <c r="O61">
-        <v>324.88609193344</v>
+        <v>323.2065341696</v>
       </c>
       <c r="P61">
-        <v>977.7846856665601</v>
+        <v>972.7298498304001</v>
       </c>
       <c r="Q61">
-        <v>2257.78468566656</v>
+        <v>2252.7298498304</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1031061531450309</v>
+        <v>0.1043670371460047</v>
       </c>
       <c r="T61">
-        <v>1.323467740069999</v>
+        <v>1.352587462956229</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.278567757315804</v>
+        <v>4.207258294693873</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06777762285840189</v>
+        <v>0.0676847617273411</v>
       </c>
       <c r="C62">
-        <v>4530.984575286512</v>
+        <v>4422.497925412157</v>
       </c>
       <c r="D62">
-        <v>10718.70457528651</v>
+        <v>10726.72992541216</v>
       </c>
       <c r="E62">
-        <v>-371.2799999999997</v>
+        <v>-254.768</v>
       </c>
       <c r="F62">
-        <v>6990.72</v>
+        <v>7107.232</v>
       </c>
       <c r="G62">
         <v>803</v>
@@ -6365,28 +6365,28 @@
         <v>1700</v>
       </c>
       <c r="M62">
-        <v>404.063616</v>
+        <v>410.7980096</v>
       </c>
       <c r="N62">
-        <v>1295.936384</v>
+        <v>1289.2019904</v>
       </c>
       <c r="O62">
-        <v>323.2065341696</v>
+        <v>321.52697640576</v>
       </c>
       <c r="P62">
-        <v>972.7298498304001</v>
+        <v>967.6750139942399</v>
       </c>
       <c r="Q62">
-        <v>2252.7298498304</v>
+        <v>2247.67501399424</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1043670371460047</v>
+        <v>0.1056925818649772</v>
       </c>
       <c r="T62">
-        <v>1.352587462956229</v>
+        <v>1.383200504964831</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.207258294693873</v>
+        <v>4.138286847239875</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0676847617273411</v>
+        <v>0.06759190059628031</v>
       </c>
       <c r="C63">
-        <v>4422.497925412157</v>
+        <v>4314.023302085003</v>
       </c>
       <c r="D63">
-        <v>10726.72992541216</v>
+        <v>10734.767302085</v>
       </c>
       <c r="E63">
-        <v>-254.768</v>
+        <v>-138.2559999999994</v>
       </c>
       <c r="F63">
-        <v>7107.232</v>
+        <v>7223.744000000001</v>
       </c>
       <c r="G63">
         <v>803</v>
@@ -6447,28 +6447,28 @@
         <v>1700</v>
       </c>
       <c r="M63">
-        <v>410.7980096</v>
+        <v>417.5324032000001</v>
       </c>
       <c r="N63">
-        <v>1289.2019904</v>
+        <v>1282.4675968</v>
       </c>
       <c r="O63">
-        <v>321.52697640576</v>
+        <v>319.84741864192</v>
       </c>
       <c r="P63">
-        <v>967.6750139942399</v>
+        <v>962.6201781580799</v>
       </c>
       <c r="Q63">
-        <v>2247.67501399424</v>
+        <v>2242.62017815808</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1056925818649772</v>
+        <v>0.1070878920954745</v>
       </c>
       <c r="T63">
-        <v>1.383200504964831</v>
+        <v>1.415424759710728</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.138286847239875</v>
+        <v>4.071540285187618</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06759190059628031</v>
+        <v>0.06749903946521951</v>
       </c>
       <c r="C64">
-        <v>4314.023302085003</v>
+        <v>4205.560732359255</v>
       </c>
       <c r="D64">
-        <v>10734.767302085</v>
+        <v>10742.81673235926</v>
       </c>
       <c r="E64">
-        <v>-138.2559999999994</v>
+        <v>-21.74399999999969</v>
       </c>
       <c r="F64">
-        <v>7223.744000000001</v>
+        <v>7340.256</v>
       </c>
       <c r="G64">
         <v>803</v>
@@ -6529,28 +6529,28 @@
         <v>1700</v>
       </c>
       <c r="M64">
-        <v>417.5324032000001</v>
+        <v>424.2667968000001</v>
       </c>
       <c r="N64">
-        <v>1282.4675968</v>
+        <v>1275.7332032</v>
       </c>
       <c r="O64">
-        <v>319.84741864192</v>
+        <v>318.16786087808</v>
       </c>
       <c r="P64">
-        <v>962.6201781580799</v>
+        <v>957.56534232192</v>
       </c>
       <c r="Q64">
-        <v>2242.62017815808</v>
+        <v>2237.56534232192</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1070878920954745</v>
+        <v>0.1085586245005933</v>
       </c>
       <c r="T64">
-        <v>1.415424759710728</v>
+        <v>1.449390866064511</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.071540285187618</v>
+        <v>4.006912661613212</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06749903946521951</v>
+        <v>0.06908752233415871</v>
       </c>
       <c r="C65">
-        <v>4205.560732359255</v>
+        <v>3952.997016907689</v>
       </c>
       <c r="D65">
-        <v>10742.81673235926</v>
+        <v>10606.76501690769</v>
       </c>
       <c r="E65">
-        <v>-21.74399999999969</v>
+        <v>94.76800000000094</v>
       </c>
       <c r="F65">
-        <v>7340.256</v>
+        <v>7456.768000000001</v>
       </c>
       <c r="G65">
         <v>803</v>
@@ -6611,45 +6611,45 @@
         <v>1700</v>
       </c>
       <c r="M65">
-        <v>424.2667968000001</v>
+        <v>457.0998784000001</v>
       </c>
       <c r="N65">
-        <v>1275.7332032</v>
+        <v>1242.9001216</v>
       </c>
       <c r="O65">
-        <v>318.16786087808</v>
+        <v>309.97929032704</v>
       </c>
       <c r="P65">
-        <v>957.56534232192</v>
+        <v>932.92083127296</v>
       </c>
       <c r="Q65">
-        <v>2237.56534232192</v>
+        <v>2212.92083127296</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1085586245005933</v>
+        <v>0.110111064261552</v>
       </c>
       <c r="T65">
-        <v>1.449390866064511</v>
+        <v>1.485243978326837</v>
       </c>
       <c r="U65">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V65">
         <v>0.2494</v>
       </c>
       <c r="W65">
-        <v>0.04338468</v>
+        <v>0.04601178</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y65">
-        <v>4.006912661613212</v>
+        <v>3.719099654873152</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06908752233415871</v>
+        <v>0.06902093220309793</v>
       </c>
       <c r="C66">
-        <v>3952.997016907689</v>
+        <v>3842.119145633118</v>
       </c>
       <c r="D66">
-        <v>10606.76501690769</v>
+        <v>10612.39914563312</v>
       </c>
       <c r="E66">
-        <v>94.76800000000094</v>
+        <v>211.2800000000007</v>
       </c>
       <c r="F66">
-        <v>7456.768000000001</v>
+        <v>7573.280000000001</v>
       </c>
       <c r="G66">
         <v>803</v>
@@ -6693,28 +6693,28 @@
         <v>1700</v>
       </c>
       <c r="M66">
-        <v>457.0998784000001</v>
+        <v>464.242064</v>
       </c>
       <c r="N66">
-        <v>1242.9001216</v>
+        <v>1235.757936</v>
       </c>
       <c r="O66">
-        <v>309.97929032704</v>
+        <v>308.1980292384</v>
       </c>
       <c r="P66">
-        <v>932.92083127296</v>
+        <v>927.5599067615999</v>
       </c>
       <c r="Q66">
-        <v>2212.92083127296</v>
+        <v>2207.5599067616</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.110111064261552</v>
+        <v>0.1117522148659941</v>
       </c>
       <c r="T66">
-        <v>1.485243978326837</v>
+        <v>1.523145839861296</v>
       </c>
       <c r="U66">
         <v>0.0613</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.719099654873152</v>
+        <v>3.661882737105873</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06902093220309793</v>
+        <v>0.06895434207203714</v>
       </c>
       <c r="C67">
-        <v>3842.119145633118</v>
+        <v>3731.24726304161</v>
       </c>
       <c r="D67">
-        <v>10612.39914563312</v>
+        <v>10618.03926304161</v>
       </c>
       <c r="E67">
-        <v>211.2800000000007</v>
+        <v>327.7920000000013</v>
       </c>
       <c r="F67">
-        <v>7573.280000000001</v>
+        <v>7689.792000000001</v>
       </c>
       <c r="G67">
         <v>803</v>
@@ -6775,28 +6775,28 @@
         <v>1700</v>
       </c>
       <c r="M67">
-        <v>464.242064</v>
+        <v>471.3842496000001</v>
       </c>
       <c r="N67">
-        <v>1235.757936</v>
+        <v>1228.6157504</v>
       </c>
       <c r="O67">
-        <v>308.1980292384</v>
+        <v>306.4167681497599</v>
       </c>
       <c r="P67">
-        <v>927.5599067615999</v>
+        <v>922.1989822502399</v>
       </c>
       <c r="Q67">
-        <v>2207.5599067616</v>
+        <v>2202.19898225024</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1117522148659941</v>
+        <v>0.1134899037412857</v>
       </c>
       <c r="T67">
-        <v>1.523145839861296</v>
+        <v>1.563277222662488</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.661882737105873</v>
+        <v>3.606399665331541</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.06895434207203714</v>
+        <v>0.06888775194097635</v>
       </c>
       <c r="C68">
-        <v>3731.24726304161</v>
+        <v>3620.381378686566</v>
       </c>
       <c r="D68">
-        <v>10618.03926304161</v>
+        <v>10623.68537868657</v>
       </c>
       <c r="E68">
-        <v>327.7920000000013</v>
+        <v>444.304000000001</v>
       </c>
       <c r="F68">
-        <v>7689.792000000001</v>
+        <v>7806.304000000001</v>
       </c>
       <c r="G68">
         <v>803</v>
@@ -6857,28 +6857,28 @@
         <v>1700</v>
       </c>
       <c r="M68">
-        <v>471.3842496000001</v>
+        <v>478.5264352</v>
       </c>
       <c r="N68">
-        <v>1228.6157504</v>
+        <v>1221.4735648</v>
       </c>
       <c r="O68">
-        <v>306.4167681497599</v>
+        <v>304.6355070611201</v>
       </c>
       <c r="P68">
-        <v>922.1989822502399</v>
+        <v>916.83805773888</v>
       </c>
       <c r="Q68">
-        <v>2202.19898225024</v>
+        <v>2196.83805773888</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1134899037412857</v>
+        <v>0.1153329070938678</v>
       </c>
       <c r="T68">
-        <v>1.563277222662488</v>
+        <v>1.605840810481934</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.606399665331541</v>
+        <v>3.552572804654952</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06888775194097635</v>
+        <v>0.06882116180991554</v>
       </c>
       <c r="C69">
-        <v>3620.381378686566</v>
+        <v>3509.521502141719</v>
       </c>
       <c r="D69">
-        <v>10623.68537868657</v>
+        <v>10629.33750214172</v>
       </c>
       <c r="E69">
-        <v>444.304000000001</v>
+        <v>560.8160000000007</v>
       </c>
       <c r="F69">
-        <v>7806.304000000001</v>
+        <v>7922.816000000001</v>
       </c>
       <c r="G69">
         <v>803</v>
@@ -6939,28 +6939,28 @@
         <v>1700</v>
       </c>
       <c r="M69">
-        <v>478.5264352</v>
+        <v>485.6686208</v>
       </c>
       <c r="N69">
-        <v>1221.4735648</v>
+        <v>1214.3313792</v>
       </c>
       <c r="O69">
-        <v>304.6355070611201</v>
+        <v>302.85424597248</v>
       </c>
       <c r="P69">
-        <v>916.83805773888</v>
+        <v>911.47713322752</v>
       </c>
       <c r="Q69">
-        <v>2196.83805773888</v>
+        <v>2191.47713322752</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1153329070938678</v>
+        <v>0.1172910981559861</v>
       </c>
       <c r="T69">
-        <v>1.605840810481934</v>
+        <v>1.651064622540096</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.552572804654952</v>
+        <v>3.500329086939437</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06882116180991554</v>
+        <v>0.07020473087885476</v>
       </c>
       <c r="C70">
-        <v>3509.521502141719</v>
+        <v>3276.795308892411</v>
       </c>
       <c r="D70">
-        <v>10629.33750214172</v>
+        <v>10513.12330889241</v>
       </c>
       <c r="E70">
-        <v>560.8160000000007</v>
+        <v>677.3280000000013</v>
       </c>
       <c r="F70">
-        <v>7922.816000000001</v>
+        <v>8039.328000000001</v>
       </c>
       <c r="G70">
         <v>803</v>
@@ -7021,45 +7021,45 @@
         <v>1700</v>
       </c>
       <c r="M70">
-        <v>485.6686208</v>
+        <v>515.3209248000002</v>
       </c>
       <c r="N70">
-        <v>1214.3313792</v>
+        <v>1184.6790752</v>
       </c>
       <c r="O70">
-        <v>302.85424597248</v>
+        <v>295.4589613548799</v>
       </c>
       <c r="P70">
-        <v>911.47713322752</v>
+        <v>889.2201138451198</v>
       </c>
       <c r="Q70">
-        <v>2191.47713322752</v>
+        <v>2169.22011384512</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1172910981559861</v>
+        <v>0.119375624125338</v>
       </c>
       <c r="T70">
-        <v>1.651064622540096</v>
+        <v>1.699206099892332</v>
       </c>
       <c r="U70">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V70">
         <v>0.2494</v>
       </c>
       <c r="W70">
-        <v>0.04601178</v>
+        <v>0.04811346</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>3.500329086939437</v>
+        <v>3.298915138483427</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07020473087885476</v>
+        <v>0.07015915754779398</v>
       </c>
       <c r="C71">
-        <v>3276.795308892411</v>
+        <v>3164.070795396198</v>
       </c>
       <c r="D71">
-        <v>10513.12330889241</v>
+        <v>10516.9107953962</v>
       </c>
       <c r="E71">
-        <v>677.3280000000013</v>
+        <v>793.8400000000011</v>
       </c>
       <c r="F71">
-        <v>8039.328000000001</v>
+        <v>8155.840000000001</v>
       </c>
       <c r="G71">
         <v>803</v>
@@ -7103,28 +7103,28 @@
         <v>1700</v>
       </c>
       <c r="M71">
-        <v>515.3209248000002</v>
+        <v>522.7893440000001</v>
       </c>
       <c r="N71">
-        <v>1184.6790752</v>
+        <v>1177.210656</v>
       </c>
       <c r="O71">
-        <v>295.4589613548799</v>
+        <v>293.5963376064</v>
       </c>
       <c r="P71">
-        <v>889.2201138451198</v>
+        <v>883.6143183935998</v>
       </c>
       <c r="Q71">
-        <v>2169.22011384512</v>
+        <v>2163.6143183936</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.119375624125338</v>
+        <v>0.1215991184926466</v>
       </c>
       <c r="T71">
-        <v>1.699206099892332</v>
+        <v>1.750557009068051</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.298915138483427</v>
+        <v>3.251787779362235</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07015915754779398</v>
+        <v>0.07011358421673319</v>
       </c>
       <c r="C72">
-        <v>3164.070795396198</v>
+        <v>3051.349011863944</v>
       </c>
       <c r="D72">
-        <v>10516.9107953962</v>
+        <v>10520.70101186394</v>
       </c>
       <c r="E72">
-        <v>793.8400000000011</v>
+        <v>910.3520000000008</v>
       </c>
       <c r="F72">
-        <v>8155.840000000001</v>
+        <v>8272.352000000001</v>
       </c>
       <c r="G72">
         <v>803</v>
@@ -7185,28 +7185,28 @@
         <v>1700</v>
       </c>
       <c r="M72">
-        <v>522.7893440000001</v>
+        <v>530.2577632000001</v>
       </c>
       <c r="N72">
-        <v>1177.210656</v>
+        <v>1169.7422368</v>
       </c>
       <c r="O72">
-        <v>293.5963376064</v>
+        <v>291.73371385792</v>
       </c>
       <c r="P72">
-        <v>883.6143183935998</v>
+        <v>878.0085229420798</v>
       </c>
       <c r="Q72">
-        <v>2163.6143183936</v>
+        <v>2158.00852294208</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1215991184926466</v>
+        <v>0.12397595729908</v>
       </c>
       <c r="T72">
-        <v>1.750557009068051</v>
+        <v>1.805449360255889</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.251787779362235</v>
+        <v>3.205987951483893</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07011358421673319</v>
+        <v>0.07006801088567241</v>
       </c>
       <c r="C73">
-        <v>3051.349011863944</v>
+        <v>2938.629961248291</v>
       </c>
       <c r="D73">
-        <v>10520.70101186394</v>
+        <v>10524.49396124829</v>
       </c>
       <c r="E73">
-        <v>910.3520000000008</v>
+        <v>1026.864</v>
       </c>
       <c r="F73">
-        <v>8272.352000000001</v>
+        <v>8388.864</v>
       </c>
       <c r="G73">
         <v>803</v>
@@ -7267,28 +7267,28 @@
         <v>1700</v>
       </c>
       <c r="M73">
-        <v>530.2577632000001</v>
+        <v>537.7261824</v>
       </c>
       <c r="N73">
-        <v>1169.7422368</v>
+        <v>1162.2738176</v>
       </c>
       <c r="O73">
-        <v>291.73371385792</v>
+        <v>289.87109010944</v>
       </c>
       <c r="P73">
-        <v>878.0085229420798</v>
+        <v>872.40272749056</v>
       </c>
       <c r="Q73">
-        <v>2158.00852294208</v>
+        <v>2152.40272749056</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.12397595729908</v>
+        <v>0.1265225703059729</v>
       </c>
       <c r="T73">
-        <v>1.805449360255889</v>
+        <v>1.864262593671429</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.205987951483893</v>
+        <v>3.161460341046618</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07006801088567241</v>
+        <v>0.0700224375546116</v>
       </c>
       <c r="C74">
-        <v>2938.629961248291</v>
+        <v>2825.913646506138</v>
       </c>
       <c r="D74">
-        <v>10524.49396124829</v>
+        <v>10528.28964650614</v>
       </c>
       <c r="E74">
-        <v>1026.864</v>
+        <v>1143.376</v>
       </c>
       <c r="F74">
-        <v>8388.864</v>
+        <v>8505.376</v>
       </c>
       <c r="G74">
         <v>803</v>
@@ -7349,28 +7349,28 @@
         <v>1700</v>
       </c>
       <c r="M74">
-        <v>537.7261824</v>
+        <v>545.1946016000001</v>
       </c>
       <c r="N74">
-        <v>1162.2738176</v>
+        <v>1154.8053984</v>
       </c>
       <c r="O74">
-        <v>289.87109010944</v>
+        <v>288.00846636096</v>
       </c>
       <c r="P74">
-        <v>872.40272749056</v>
+        <v>866.7969320390398</v>
       </c>
       <c r="Q74">
-        <v>2152.40272749056</v>
+        <v>2146.79693203904</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1265225703059729</v>
+        <v>0.1292578213133763</v>
       </c>
       <c r="T74">
-        <v>1.864262593671429</v>
+        <v>1.927432362895527</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.161460341046618</v>
+        <v>3.118152665141869</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.0700224375546116</v>
+        <v>0.0699768642235508</v>
       </c>
       <c r="C75">
-        <v>2825.913646506138</v>
+        <v>2713.20007059865</v>
       </c>
       <c r="D75">
-        <v>10528.28964650614</v>
+        <v>10532.08807059865</v>
       </c>
       <c r="E75">
-        <v>1143.376</v>
+        <v>1259.888000000001</v>
       </c>
       <c r="F75">
-        <v>8505.376</v>
+        <v>8621.888000000001</v>
       </c>
       <c r="G75">
         <v>803</v>
@@ -7431,28 +7431,28 @@
         <v>1700</v>
       </c>
       <c r="M75">
-        <v>545.1946016000001</v>
+        <v>552.6630208000001</v>
       </c>
       <c r="N75">
-        <v>1154.8053984</v>
+        <v>1147.3369792</v>
       </c>
       <c r="O75">
-        <v>288.00846636096</v>
+        <v>286.14584261248</v>
       </c>
       <c r="P75">
-        <v>866.7969320390398</v>
+        <v>861.1911365875198</v>
       </c>
       <c r="Q75">
-        <v>2146.79693203904</v>
+        <v>2141.19113658752</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1292578213133763</v>
+        <v>0.1322034762444262</v>
       </c>
       <c r="T75">
-        <v>1.927432362895527</v>
+        <v>1.995461345136864</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.118152665141869</v>
+        <v>3.076015466964277</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.0699768642235508</v>
+        <v>0.06993129089249003</v>
       </c>
       <c r="C76">
-        <v>2713.20007059865</v>
+        <v>2600.489236491268</v>
       </c>
       <c r="D76">
-        <v>10532.08807059865</v>
+        <v>10535.88923649127</v>
       </c>
       <c r="E76">
-        <v>1259.888000000001</v>
+        <v>1376.400000000001</v>
       </c>
       <c r="F76">
-        <v>8621.888000000001</v>
+        <v>8738.400000000001</v>
       </c>
       <c r="G76">
         <v>803</v>
@@ -7513,28 +7513,28 @@
         <v>1700</v>
       </c>
       <c r="M76">
-        <v>552.6630208000001</v>
+        <v>560.1314400000001</v>
       </c>
       <c r="N76">
-        <v>1147.3369792</v>
+        <v>1139.86856</v>
       </c>
       <c r="O76">
-        <v>286.14584261248</v>
+        <v>284.283218864</v>
       </c>
       <c r="P76">
-        <v>861.1911365875198</v>
+        <v>855.5853411359999</v>
       </c>
       <c r="Q76">
-        <v>2141.19113658752</v>
+        <v>2135.585341136</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1322034762444262</v>
+        <v>0.1353847835699601</v>
       </c>
       <c r="T76">
-        <v>1.995461345136864</v>
+        <v>2.068932645957509</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.076015466964277</v>
+        <v>3.035001927404753</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.06993129089249003</v>
+        <v>0.07433527436142923</v>
       </c>
       <c r="C77">
-        <v>2600.489236491268</v>
+        <v>2128.902500430217</v>
       </c>
       <c r="D77">
-        <v>10535.88923649127</v>
+        <v>10180.81450043022</v>
       </c>
       <c r="E77">
-        <v>1376.400000000001</v>
+        <v>1492.912</v>
       </c>
       <c r="F77">
-        <v>8738.400000000001</v>
+        <v>8854.912</v>
       </c>
       <c r="G77">
         <v>803</v>
@@ -7595,45 +7595,45 @@
         <v>1700</v>
       </c>
       <c r="M77">
-        <v>560.1314400000001</v>
+        <v>636.6681728000001</v>
       </c>
       <c r="N77">
-        <v>1139.86856</v>
+        <v>1063.3318272</v>
       </c>
       <c r="O77">
-        <v>284.283218864</v>
+        <v>265.19495770368</v>
       </c>
       <c r="P77">
-        <v>855.5853411359999</v>
+        <v>798.1368694963199</v>
       </c>
       <c r="Q77">
-        <v>2135.585341136</v>
+        <v>2078.13686949632</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1353847835699601</v>
+        <v>0.1388311998392885</v>
       </c>
       <c r="T77">
-        <v>2.068932645957509</v>
+        <v>2.148526555179873</v>
       </c>
       <c r="U77">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V77">
         <v>0.2494</v>
       </c>
       <c r="W77">
-        <v>0.04811346</v>
+        <v>0.05396814</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.035001927404753</v>
+        <v>2.670150751408819</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07433527436142923</v>
+        <v>0.07434824783036845</v>
       </c>
       <c r="C78">
-        <v>2128.902500430217</v>
+        <v>2011.379855915893</v>
       </c>
       <c r="D78">
-        <v>10180.81450043022</v>
+        <v>10179.80385591589</v>
       </c>
       <c r="E78">
-        <v>1492.912</v>
+        <v>1609.424000000001</v>
       </c>
       <c r="F78">
-        <v>8854.912</v>
+        <v>8971.424000000001</v>
       </c>
       <c r="G78">
         <v>803</v>
@@ -7677,28 +7677,28 @@
         <v>1700</v>
       </c>
       <c r="M78">
-        <v>636.6681728000001</v>
+        <v>645.0453856000001</v>
       </c>
       <c r="N78">
-        <v>1063.3318272</v>
+        <v>1054.9546144</v>
       </c>
       <c r="O78">
-        <v>265.19495770368</v>
+        <v>263.10568083136</v>
       </c>
       <c r="P78">
-        <v>798.1368694963199</v>
+        <v>791.8489335686399</v>
       </c>
       <c r="Q78">
-        <v>2078.13686949632</v>
+        <v>2071.84893356864</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1388311998392885</v>
+        <v>0.1425773044798628</v>
       </c>
       <c r="T78">
-        <v>2.148526555179873</v>
+        <v>2.235041673899834</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.670150751408819</v>
+        <v>2.63547346892299</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07434824783036845</v>
+        <v>0.07436122129930764</v>
       </c>
       <c r="C79">
-        <v>2011.379855915893</v>
+        <v>1893.857412034038</v>
       </c>
       <c r="D79">
-        <v>10179.80385591589</v>
+        <v>10178.79341203404</v>
       </c>
       <c r="E79">
-        <v>1609.424000000001</v>
+        <v>1725.936000000002</v>
       </c>
       <c r="F79">
-        <v>8971.424000000001</v>
+        <v>9087.936000000002</v>
       </c>
       <c r="G79">
         <v>803</v>
@@ -7759,28 +7759,28 @@
         <v>1700</v>
       </c>
       <c r="M79">
-        <v>645.0453856000001</v>
+        <v>653.4225984000002</v>
       </c>
       <c r="N79">
-        <v>1054.9546144</v>
+        <v>1046.5774016</v>
       </c>
       <c r="O79">
-        <v>263.10568083136</v>
+        <v>261.01640395904</v>
       </c>
       <c r="P79">
-        <v>791.8489335686399</v>
+        <v>785.5609976409598</v>
       </c>
       <c r="Q79">
-        <v>2071.84893356864</v>
+        <v>2065.56099764096</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1425773044798628</v>
+        <v>0.1466639640877621</v>
       </c>
       <c r="T79">
-        <v>2.235041673899834</v>
+        <v>2.329421803412519</v>
       </c>
       <c r="U79">
         <v>0.07190000000000001</v>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.63547346892299</v>
+        <v>2.601685347526541</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07436122129930764</v>
+        <v>0.07437419476824686</v>
       </c>
       <c r="C80">
-        <v>1893.857412034038</v>
+        <v>1776.335168724907</v>
       </c>
       <c r="D80">
-        <v>10178.79341203404</v>
+        <v>10177.78316872491</v>
       </c>
       <c r="E80">
-        <v>1725.936000000002</v>
+        <v>1842.448</v>
       </c>
       <c r="F80">
-        <v>9087.936000000002</v>
+        <v>9204.448</v>
       </c>
       <c r="G80">
         <v>803</v>
@@ -7841,28 +7841,28 @@
         <v>1700</v>
       </c>
       <c r="M80">
-        <v>653.4225984000002</v>
+        <v>661.7998112</v>
       </c>
       <c r="N80">
-        <v>1046.5774016</v>
+        <v>1038.2001888</v>
       </c>
       <c r="O80">
-        <v>261.01640395904</v>
+        <v>258.92712708672</v>
       </c>
       <c r="P80">
-        <v>785.5609976409598</v>
+        <v>779.27306171328</v>
       </c>
       <c r="Q80">
-        <v>2065.56099764096</v>
+        <v>2059.27306171328</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1466639640877621</v>
+        <v>0.1511398293726041</v>
       </c>
       <c r="T80">
-        <v>2.329421803412519</v>
+        <v>2.432790516688317</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.601685347526541</v>
+        <v>2.568752621608485</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07437419476824686</v>
+        <v>0.07438716823718607</v>
       </c>
       <c r="C81">
-        <v>1776.335168724907</v>
+        <v>1658.813125928787</v>
       </c>
       <c r="D81">
-        <v>10177.78316872491</v>
+        <v>10176.77312592879</v>
       </c>
       <c r="E81">
-        <v>1842.448</v>
+        <v>1958.960000000001</v>
       </c>
       <c r="F81">
-        <v>9204.448</v>
+        <v>9320.960000000001</v>
       </c>
       <c r="G81">
         <v>803</v>
@@ -7923,28 +7923,28 @@
         <v>1700</v>
       </c>
       <c r="M81">
-        <v>661.7998112</v>
+        <v>670.1770240000001</v>
       </c>
       <c r="N81">
-        <v>1038.2001888</v>
+        <v>1029.822976</v>
       </c>
       <c r="O81">
-        <v>258.92712708672</v>
+        <v>256.8378502144</v>
       </c>
       <c r="P81">
-        <v>779.27306171328</v>
+        <v>772.9851257855998</v>
       </c>
       <c r="Q81">
-        <v>2059.27306171328</v>
+        <v>2052.9851257856</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1511398293726041</v>
+        <v>0.1560632811859304</v>
       </c>
       <c r="T81">
-        <v>2.432790516688317</v>
+        <v>2.546496101291695</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.568752621608485</v>
+        <v>2.536643213838378</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07438716823718607</v>
+        <v>0.07440014170612527</v>
       </c>
       <c r="C82">
-        <v>1658.813125928787</v>
+        <v>1541.29128358599</v>
       </c>
       <c r="D82">
-        <v>10176.77312592879</v>
+        <v>10175.76328358599</v>
       </c>
       <c r="E82">
-        <v>1958.960000000001</v>
+        <v>2075.472000000002</v>
       </c>
       <c r="F82">
-        <v>9320.960000000001</v>
+        <v>9437.472000000002</v>
       </c>
       <c r="G82">
         <v>803</v>
@@ -8005,28 +8005,28 @@
         <v>1700</v>
       </c>
       <c r="M82">
-        <v>670.1770240000001</v>
+        <v>678.5542368000001</v>
       </c>
       <c r="N82">
-        <v>1029.822976</v>
+        <v>1021.4457632</v>
       </c>
       <c r="O82">
-        <v>256.8378502144</v>
+        <v>254.74857334208</v>
       </c>
       <c r="P82">
-        <v>772.9851257855998</v>
+        <v>766.6971898579199</v>
       </c>
       <c r="Q82">
-        <v>2052.9851257856</v>
+        <v>2046.69718985792</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1560632811859304</v>
+        <v>0.1615049910848699</v>
       </c>
       <c r="T82">
-        <v>2.546496101291695</v>
+        <v>2.672170694800691</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.536643213838378</v>
+        <v>2.505326630951484</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07440014170612527</v>
+        <v>0.07681353397506449</v>
       </c>
       <c r="C83">
-        <v>1541.29128358599</v>
+        <v>1240.346296135838</v>
       </c>
       <c r="D83">
-        <v>10175.76328358599</v>
+        <v>9991.33029613584</v>
       </c>
       <c r="E83">
-        <v>2075.472000000002</v>
+        <v>2191.984000000002</v>
       </c>
       <c r="F83">
-        <v>9437.472000000002</v>
+        <v>9553.984000000002</v>
       </c>
       <c r="G83">
         <v>803</v>
@@ -8087,45 +8087,45 @@
         <v>1700</v>
       </c>
       <c r="M83">
-        <v>678.5542368000001</v>
+        <v>724.1919872000002</v>
       </c>
       <c r="N83">
-        <v>1021.4457632</v>
+        <v>975.8080127999998</v>
       </c>
       <c r="O83">
-        <v>254.74857334208</v>
+        <v>243.36651839232</v>
       </c>
       <c r="P83">
-        <v>766.6971898579199</v>
+        <v>732.4414944076798</v>
       </c>
       <c r="Q83">
-        <v>2046.69718985792</v>
+        <v>2012.44149440768</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1615049910848699</v>
+        <v>0.167551335417025</v>
       </c>
       <c r="T83">
-        <v>2.672170694800691</v>
+        <v>2.81180913203291</v>
       </c>
       <c r="U83">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V83">
         <v>0.2494</v>
       </c>
       <c r="W83">
-        <v>0.05396814</v>
+        <v>0.05689548</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y83">
-        <v>2.505326630951484</v>
+        <v>2.347443813308184</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07681353397506449</v>
+        <v>0.07685578084400368</v>
       </c>
       <c r="C84">
-        <v>1240.346296135838</v>
+        <v>1120.665285021909</v>
       </c>
       <c r="D84">
-        <v>9991.33029613584</v>
+        <v>9988.16128502191</v>
       </c>
       <c r="E84">
-        <v>2191.984000000002</v>
+        <v>2308.496000000001</v>
       </c>
       <c r="F84">
-        <v>9553.984000000002</v>
+        <v>9670.496000000001</v>
       </c>
       <c r="G84">
         <v>803</v>
@@ -8169,28 +8169,28 @@
         <v>1700</v>
       </c>
       <c r="M84">
-        <v>724.1919872000002</v>
+        <v>733.0235968000002</v>
       </c>
       <c r="N84">
-        <v>975.8080127999998</v>
+        <v>966.9764031999998</v>
       </c>
       <c r="O84">
-        <v>243.36651839232</v>
+        <v>241.16391495808</v>
       </c>
       <c r="P84">
-        <v>732.4414944076798</v>
+        <v>725.8124882419198</v>
       </c>
       <c r="Q84">
-        <v>2012.44149440768</v>
+        <v>2005.81248824192</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.167551335417025</v>
+        <v>0.1743090143764924</v>
       </c>
       <c r="T84">
-        <v>2.81180913203291</v>
+        <v>2.967875620704212</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.347443813308184</v>
+        <v>2.319161357726157</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07685578084400368</v>
+        <v>0.07689802771294291</v>
       </c>
       <c r="C85">
-        <v>1120.665285021909</v>
+        <v>1000.986283539698</v>
       </c>
       <c r="D85">
-        <v>9988.16128502191</v>
+        <v>9984.9942835397</v>
       </c>
       <c r="E85">
-        <v>2308.496000000001</v>
+        <v>2425.008000000002</v>
       </c>
       <c r="F85">
-        <v>9670.496000000001</v>
+        <v>9787.008000000002</v>
       </c>
       <c r="G85">
         <v>803</v>
@@ -8251,28 +8251,28 @@
         <v>1700</v>
       </c>
       <c r="M85">
-        <v>733.0235968000002</v>
+        <v>741.8552064000002</v>
       </c>
       <c r="N85">
-        <v>966.9764031999998</v>
+        <v>958.1447935999998</v>
       </c>
       <c r="O85">
-        <v>241.16391495808</v>
+        <v>238.96131152384</v>
       </c>
       <c r="P85">
-        <v>725.8124882419198</v>
+        <v>719.1834820761599</v>
       </c>
       <c r="Q85">
-        <v>2005.81248824192</v>
+        <v>1999.18348207616</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1743090143764924</v>
+        <v>0.1819114032058932</v>
       </c>
       <c r="T85">
-        <v>2.967875620704212</v>
+        <v>3.143450420459428</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.319161357726157</v>
+        <v>2.291552293943703</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07689802771294291</v>
+        <v>0.07694027458188211</v>
       </c>
       <c r="C86">
-        <v>1000.9862835397</v>
+        <v>881.309289778208</v>
       </c>
       <c r="D86">
-        <v>9984.9942835397</v>
+        <v>9981.829289778208</v>
       </c>
       <c r="E86">
-        <v>2425.008</v>
+        <v>2541.52</v>
       </c>
       <c r="F86">
-        <v>9787.008</v>
+        <v>9903.52</v>
       </c>
       <c r="G86">
         <v>803</v>
@@ -8333,28 +8333,28 @@
         <v>1700</v>
       </c>
       <c r="M86">
-        <v>741.8552064</v>
+        <v>750.6868160000001</v>
       </c>
       <c r="N86">
-        <v>958.1447936</v>
+        <v>949.3131839999999</v>
       </c>
       <c r="O86">
-        <v>238.96131152384</v>
+        <v>236.7587080896</v>
       </c>
       <c r="P86">
-        <v>719.18348207616</v>
+        <v>712.5544759103999</v>
       </c>
       <c r="Q86">
-        <v>1999.18348207616</v>
+        <v>1992.5544759104</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1819114032058931</v>
+        <v>0.1905274438792141</v>
       </c>
       <c r="T86">
-        <v>3.143450420459426</v>
+        <v>3.342435193515337</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.291552293943704</v>
+        <v>2.264592855191425</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07694027458188211</v>
+        <v>0.07698252145082132</v>
       </c>
       <c r="C87">
-        <v>881.309289778208</v>
+        <v>761.6343018288426</v>
       </c>
       <c r="D87">
-        <v>9981.829289778208</v>
+        <v>9978.666301828844</v>
       </c>
       <c r="E87">
-        <v>2541.52</v>
+        <v>2658.032000000001</v>
       </c>
       <c r="F87">
-        <v>9903.52</v>
+        <v>10020.032</v>
       </c>
       <c r="G87">
         <v>803</v>
@@ -8415,28 +8415,28 @@
         <v>1700</v>
       </c>
       <c r="M87">
-        <v>750.6868160000001</v>
+        <v>759.5184256000001</v>
       </c>
       <c r="N87">
-        <v>949.3131839999999</v>
+        <v>940.4815743999999</v>
       </c>
       <c r="O87">
-        <v>236.7587080896</v>
+        <v>234.55610465536</v>
       </c>
       <c r="P87">
-        <v>712.5544759103999</v>
+        <v>705.9254697446399</v>
       </c>
       <c r="Q87">
-        <v>1992.5544759104</v>
+        <v>1985.92546974464</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.1905274438792141</v>
+        <v>0.2003743475058666</v>
       </c>
       <c r="T87">
-        <v>3.342435193515337</v>
+        <v>3.569846362722092</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.264592855191425</v>
+        <v>2.238260380131059</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07698252145082132</v>
+        <v>0.07702476831976052</v>
       </c>
       <c r="C88">
-        <v>761.6343018288426</v>
+        <v>641.9613177854408</v>
       </c>
       <c r="D88">
-        <v>9978.666301828844</v>
+        <v>9975.505317785441</v>
       </c>
       <c r="E88">
-        <v>2658.032000000001</v>
+        <v>2774.544</v>
       </c>
       <c r="F88">
-        <v>10020.032</v>
+        <v>10136.544</v>
       </c>
       <c r="G88">
         <v>803</v>
@@ -8497,28 +8497,28 @@
         <v>1700</v>
       </c>
       <c r="M88">
-        <v>759.5184256000001</v>
+        <v>768.3500352000001</v>
       </c>
       <c r="N88">
-        <v>940.4815743999999</v>
+        <v>931.6499647999999</v>
       </c>
       <c r="O88">
-        <v>234.55610465536</v>
+        <v>232.35350122112</v>
       </c>
       <c r="P88">
-        <v>705.9254697446399</v>
+        <v>699.2964635788799</v>
       </c>
       <c r="Q88">
-        <v>1985.92546974464</v>
+        <v>1979.29646357888</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2003743475058666</v>
+        <v>0.2117361593827733</v>
       </c>
       <c r="T88">
-        <v>3.569846362722092</v>
+        <v>3.832243865652964</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.238260380131059</v>
+        <v>2.212533249324955</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07702476831976052</v>
+        <v>0.07706701518869974</v>
       </c>
       <c r="C89">
-        <v>641.9613177854408</v>
+        <v>522.290335744241</v>
       </c>
       <c r="D89">
-        <v>9975.505317785441</v>
+        <v>9972.346335744242</v>
       </c>
       <c r="E89">
-        <v>2774.544</v>
+        <v>2891.056</v>
       </c>
       <c r="F89">
-        <v>10136.544</v>
+        <v>10253.056</v>
       </c>
       <c r="G89">
         <v>803</v>
@@ -8579,28 +8579,28 @@
         <v>1700</v>
       </c>
       <c r="M89">
-        <v>768.3500352000001</v>
+        <v>777.1816448000001</v>
       </c>
       <c r="N89">
-        <v>931.6499647999999</v>
+        <v>922.8183551999999</v>
       </c>
       <c r="O89">
-        <v>232.35350122112</v>
+        <v>230.15089778688</v>
       </c>
       <c r="P89">
-        <v>699.2964635788799</v>
+        <v>692.6674574131199</v>
       </c>
       <c r="Q89">
-        <v>1979.29646357888</v>
+        <v>1972.66745741312</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2117361593827733</v>
+        <v>0.2249916065724979</v>
       </c>
       <c r="T89">
-        <v>3.832243865652964</v>
+        <v>4.138374285738982</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.212533249324955</v>
+        <v>2.187390826037172</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07706701518869974</v>
+        <v>0.07710926205763895</v>
       </c>
       <c r="C90">
-        <v>522.290335744241</v>
+        <v>402.6213538039046</v>
       </c>
       <c r="D90">
-        <v>9972.346335744242</v>
+        <v>9969.189353803906</v>
       </c>
       <c r="E90">
-        <v>2891.056</v>
+        <v>3007.568000000001</v>
       </c>
       <c r="F90">
-        <v>10253.056</v>
+        <v>10369.568</v>
       </c>
       <c r="G90">
         <v>803</v>
@@ -8661,28 +8661,28 @@
         <v>1700</v>
       </c>
       <c r="M90">
-        <v>777.1816448000001</v>
+        <v>786.0132544000002</v>
       </c>
       <c r="N90">
-        <v>922.8183551999999</v>
+        <v>913.9867455999998</v>
       </c>
       <c r="O90">
-        <v>230.15089778688</v>
+        <v>227.94829435264</v>
       </c>
       <c r="P90">
-        <v>692.6674574131199</v>
+        <v>686.0384512473598</v>
       </c>
       <c r="Q90">
-        <v>1972.66745741312</v>
+        <v>1966.03845124736</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2249916065724979</v>
+        <v>0.240657135069445</v>
       </c>
       <c r="T90">
-        <v>4.138374285738982</v>
+        <v>4.500164782204274</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.187390826037172</v>
+        <v>2.162813401025518</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.07710926205763895</v>
+        <v>0.07715150892657816</v>
       </c>
       <c r="C91">
-        <v>402.6213538039046</v>
+        <v>282.9543700654958</v>
       </c>
       <c r="D91">
-        <v>9969.189353803906</v>
+        <v>9966.034370065498</v>
       </c>
       <c r="E91">
-        <v>3007.568000000001</v>
+        <v>3124.080000000002</v>
       </c>
       <c r="F91">
-        <v>10369.568</v>
+        <v>10486.08</v>
       </c>
       <c r="G91">
         <v>803</v>
@@ -8743,28 +8743,28 @@
         <v>1700</v>
       </c>
       <c r="M91">
-        <v>786.0132544000002</v>
+        <v>794.8448640000001</v>
       </c>
       <c r="N91">
-        <v>913.9867455999998</v>
+        <v>905.1551359999999</v>
       </c>
       <c r="O91">
-        <v>227.94829435264</v>
+        <v>225.7456909184</v>
       </c>
       <c r="P91">
-        <v>686.0384512473598</v>
+        <v>679.4094450815999</v>
       </c>
       <c r="Q91">
-        <v>1966.03845124736</v>
+        <v>1959.4094450816</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.240657135069445</v>
+        <v>0.2594557692657816</v>
       </c>
       <c r="T91">
-        <v>4.500164782204274</v>
+        <v>4.934313377962624</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.162813401025518</v>
+        <v>2.138782141014123</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07715150892657816</v>
+        <v>0.07719375579551736</v>
       </c>
       <c r="C92">
-        <v>282.9543700654958</v>
+        <v>163.2893826324798</v>
       </c>
       <c r="D92">
-        <v>9966.034370065498</v>
+        <v>9962.88138263248</v>
       </c>
       <c r="E92">
-        <v>3124.080000000002</v>
+        <v>3240.592000000001</v>
       </c>
       <c r="F92">
-        <v>10486.08</v>
+        <v>10602.592</v>
       </c>
       <c r="G92">
         <v>803</v>
@@ -8825,28 +8825,28 @@
         <v>1700</v>
       </c>
       <c r="M92">
-        <v>794.8448640000001</v>
+        <v>803.6764736000001</v>
       </c>
       <c r="N92">
-        <v>905.1551359999999</v>
+        <v>896.3235263999999</v>
       </c>
       <c r="O92">
-        <v>225.7456909184</v>
+        <v>223.54308748416</v>
       </c>
       <c r="P92">
-        <v>679.4094450815999</v>
+        <v>672.7804389158399</v>
       </c>
       <c r="Q92">
-        <v>1959.4094450816</v>
+        <v>1952.78043891584</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2594557692657816</v>
+        <v>0.2824318777279708</v>
       </c>
       <c r="T92">
-        <v>4.934313377962624</v>
+        <v>5.464939439445054</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.138782141014123</v>
+        <v>2.115279040563419</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07719375579551736</v>
+        <v>0.07723600266445657</v>
       </c>
       <c r="C93">
-        <v>163.2893826324798</v>
+        <v>43.62638961072116</v>
       </c>
       <c r="D93">
-        <v>9962.88138263248</v>
+        <v>9959.730389610722</v>
       </c>
       <c r="E93">
-        <v>3240.592000000001</v>
+        <v>3357.104000000001</v>
       </c>
       <c r="F93">
-        <v>10602.592</v>
+        <v>10719.104</v>
       </c>
       <c r="G93">
         <v>803</v>
@@ -8907,28 +8907,28 @@
         <v>1700</v>
       </c>
       <c r="M93">
-        <v>803.6764736000001</v>
+        <v>812.5080832000001</v>
       </c>
       <c r="N93">
-        <v>896.3235263999999</v>
+        <v>887.4919167999999</v>
       </c>
       <c r="O93">
-        <v>223.54308748416</v>
+        <v>221.34048404992</v>
       </c>
       <c r="P93">
-        <v>672.7804389158399</v>
+        <v>666.1514327500799</v>
       </c>
       <c r="Q93">
-        <v>1952.78043891584</v>
+        <v>1946.15143275008</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.2824318777279708</v>
+        <v>0.3111520133057074</v>
       </c>
       <c r="T93">
-        <v>5.464939439445054</v>
+        <v>6.128222016298093</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.115279040563419</v>
+        <v>2.092286877079034</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07723600266445657</v>
+        <v>0.07727824953339579</v>
       </c>
       <c r="C94">
-        <v>43.62638961072116</v>
+        <v>-76.03461089151824</v>
       </c>
       <c r="D94">
-        <v>9959.730389610722</v>
+        <v>9956.581389108484</v>
       </c>
       <c r="E94">
-        <v>3357.104000000001</v>
+        <v>3473.616000000002</v>
       </c>
       <c r="F94">
-        <v>10719.104</v>
+        <v>10835.616</v>
       </c>
       <c r="G94">
         <v>803</v>
@@ -8989,28 +8989,28 @@
         <v>1700</v>
       </c>
       <c r="M94">
-        <v>812.5080832000001</v>
+        <v>821.3396928000002</v>
       </c>
       <c r="N94">
-        <v>887.4919167999999</v>
+        <v>878.6603071999998</v>
       </c>
       <c r="O94">
-        <v>221.34048404992</v>
+        <v>219.13788061568</v>
       </c>
       <c r="P94">
-        <v>666.1514327500799</v>
+        <v>659.5224265843199</v>
       </c>
       <c r="Q94">
-        <v>1946.15143275008</v>
+        <v>1939.52242658432</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3111520133057074</v>
+        <v>0.3480779019056543</v>
       </c>
       <c r="T94">
-        <v>6.128222016298093</v>
+        <v>6.981013900823426</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.092286877079034</v>
+        <v>2.069789168723345</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07727824953339579</v>
+        <v>0.07732049640233499</v>
       </c>
       <c r="C95">
-        <v>-76.03461089151824</v>
+        <v>-195.6936207635808</v>
       </c>
       <c r="D95">
-        <v>9956.581389108484</v>
+        <v>9953.43437923642</v>
       </c>
       <c r="E95">
-        <v>3473.616000000002</v>
+        <v>3590.128000000001</v>
       </c>
       <c r="F95">
-        <v>10835.616</v>
+        <v>10952.128</v>
       </c>
       <c r="G95">
         <v>803</v>
@@ -9071,28 +9071,28 @@
         <v>1700</v>
       </c>
       <c r="M95">
-        <v>821.3396928000002</v>
+        <v>830.1713024000001</v>
       </c>
       <c r="N95">
-        <v>878.6603071999998</v>
+        <v>869.8286975999999</v>
       </c>
       <c r="O95">
-        <v>219.13788061568</v>
+        <v>216.93527718144</v>
       </c>
       <c r="P95">
-        <v>659.5224265843199</v>
+        <v>652.8934204185599</v>
       </c>
       <c r="Q95">
-        <v>1939.52242658432</v>
+        <v>1932.89342041856</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3480779019056543</v>
+        <v>0.3973124200389169</v>
       </c>
       <c r="T95">
-        <v>6.981013900823426</v>
+        <v>8.118069746857204</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.069789168723345</v>
+        <v>2.047770135013523</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.07732049640233499</v>
+        <v>0.07736274327127421</v>
       </c>
       <c r="C96">
-        <v>-195.6936207635808</v>
+        <v>-315.3506418924335</v>
       </c>
       <c r="D96">
-        <v>9953.43437923642</v>
+        <v>9950.289358107568</v>
       </c>
       <c r="E96">
-        <v>3590.128000000001</v>
+        <v>3706.640000000001</v>
       </c>
       <c r="F96">
-        <v>10952.128</v>
+        <v>11068.64</v>
       </c>
       <c r="G96">
         <v>803</v>
@@ -9153,28 +9153,28 @@
         <v>1700</v>
       </c>
       <c r="M96">
-        <v>830.1713024000001</v>
+        <v>839.0029120000002</v>
       </c>
       <c r="N96">
-        <v>869.8286975999999</v>
+        <v>860.9970879999998</v>
       </c>
       <c r="O96">
-        <v>216.93527718144</v>
+        <v>214.7326737472</v>
       </c>
       <c r="P96">
-        <v>652.8934204185599</v>
+        <v>646.2644142527998</v>
       </c>
       <c r="Q96">
-        <v>1932.89342041856</v>
+        <v>1926.2644142528</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.3973124200389169</v>
+        <v>0.4662407454254846</v>
       </c>
       <c r="T96">
-        <v>8.118069746857204</v>
+        <v>9.709947931304496</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.047770135013523</v>
+        <v>2.026214659908117</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07736274327127421</v>
+        <v>0.0774049901402134</v>
       </c>
       <c r="C97">
-        <v>-315.3506418924335</v>
+        <v>-435.0056761626438</v>
       </c>
       <c r="D97">
-        <v>9950.289358107568</v>
+        <v>9947.146323837358</v>
       </c>
       <c r="E97">
-        <v>3706.640000000001</v>
+        <v>3823.152000000002</v>
       </c>
       <c r="F97">
-        <v>11068.64</v>
+        <v>11185.152</v>
       </c>
       <c r="G97">
         <v>803</v>
@@ -9235,28 +9235,28 @@
         <v>1700</v>
       </c>
       <c r="M97">
-        <v>839.0029120000002</v>
+        <v>847.8345216000002</v>
       </c>
       <c r="N97">
-        <v>860.9970879999998</v>
+        <v>852.1654783999998</v>
       </c>
       <c r="O97">
-        <v>214.7326737472</v>
+        <v>212.5300703129599</v>
       </c>
       <c r="P97">
-        <v>646.2644142527998</v>
+        <v>639.6354080870399</v>
       </c>
       <c r="Q97">
-        <v>1926.2644142528</v>
+        <v>1919.63540808704</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.4662407454254846</v>
+        <v>0.5696332335053362</v>
       </c>
       <c r="T97">
-        <v>9.709947931304496</v>
+        <v>12.09776520797543</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.026214659908117</v>
+        <v>2.005108257200741</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.0774049901402134</v>
+        <v>0.0877860014091526</v>
       </c>
       <c r="C98">
-        <v>-435.005676162642</v>
+        <v>-1267.978572385255</v>
       </c>
       <c r="D98">
-        <v>9947.146323837358</v>
+        <v>9230.685427614746</v>
       </c>
       <c r="E98">
-        <v>3823.152</v>
+        <v>3939.664000000001</v>
       </c>
       <c r="F98">
-        <v>11185.152</v>
+        <v>11301.664</v>
       </c>
       <c r="G98">
         <v>803</v>
@@ -9317,45 +9317,45 @@
         <v>1700</v>
       </c>
       <c r="M98">
-        <v>847.8345216000001</v>
+        <v>1017.14976</v>
       </c>
       <c r="N98">
-        <v>852.1654783999999</v>
+        <v>682.85024</v>
       </c>
       <c r="O98">
-        <v>212.53007031296</v>
+        <v>170.302849856</v>
       </c>
       <c r="P98">
-        <v>639.6354080870399</v>
+        <v>512.547390144</v>
       </c>
       <c r="Q98">
-        <v>1919.63540808704</v>
+        <v>1792.547390144</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.5696332335053347</v>
+        <v>0.7419540469717535</v>
       </c>
       <c r="T98">
-        <v>12.0977652079754</v>
+        <v>16.07746066909362</v>
       </c>
       <c r="U98">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V98">
         <v>0.2494</v>
       </c>
       <c r="W98">
-        <v>0.05689548</v>
+        <v>0.06755399999999999</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y98">
-        <v>2.005108257200741</v>
+        <v>1.671336972050212</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.0877860014091526</v>
+        <v>0.08793483347809182</v>
       </c>
       <c r="C99">
-        <v>-1267.978572385255</v>
+        <v>-1394.012756017939</v>
       </c>
       <c r="D99">
-        <v>9230.685427614746</v>
+        <v>9221.163243982062</v>
       </c>
       <c r="E99">
-        <v>3939.664000000001</v>
+        <v>4056.176000000001</v>
       </c>
       <c r="F99">
-        <v>11301.664</v>
+        <v>11418.176</v>
       </c>
       <c r="G99">
         <v>803</v>
@@ -9399,28 +9399,28 @@
         <v>1700</v>
       </c>
       <c r="M99">
-        <v>1017.14976</v>
+        <v>1027.63584</v>
       </c>
       <c r="N99">
-        <v>682.85024</v>
+        <v>672.3641599999999</v>
       </c>
       <c r="O99">
-        <v>170.302849856</v>
+        <v>167.687621504</v>
       </c>
       <c r="P99">
-        <v>512.547390144</v>
+        <v>504.6765384959999</v>
       </c>
       <c r="Q99">
-        <v>1792.547390144</v>
+        <v>1784.676538496</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.7419540469717535</v>
+        <v>1.086595673904591</v>
       </c>
       <c r="T99">
-        <v>16.07746066909362</v>
+        <v>24.03685159133004</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.671336972050212</v>
+        <v>1.65428251315174</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08793483347809182</v>
+        <v>0.08808366554703102</v>
       </c>
       <c r="C100">
-        <v>-1394.012756017939</v>
+        <v>-1520.027314121642</v>
       </c>
       <c r="D100">
-        <v>9221.163243982062</v>
+        <v>9211.660685878358</v>
       </c>
       <c r="E100">
-        <v>4056.176000000001</v>
+        <v>4172.688</v>
       </c>
       <c r="F100">
-        <v>11418.176</v>
+        <v>11534.688</v>
       </c>
       <c r="G100">
         <v>803</v>
@@ -9481,28 +9481,28 @@
         <v>1700</v>
       </c>
       <c r="M100">
-        <v>1027.63584</v>
+        <v>1038.12192</v>
       </c>
       <c r="N100">
-        <v>672.3641599999999</v>
+        <v>661.87808</v>
       </c>
       <c r="O100">
-        <v>167.687621504</v>
+        <v>165.072393152</v>
       </c>
       <c r="P100">
-        <v>504.6765384959999</v>
+        <v>496.8056868479999</v>
       </c>
       <c r="Q100">
-        <v>1784.676538496</v>
+        <v>1776.805686848</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.086595673904591</v>
+        <v>2.120520554703102</v>
       </c>
       <c r="T100">
-        <v>24.03685159133004</v>
+        <v>47.91502435803931</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.65428251315174</v>
+        <v>1.63757258877647</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08808366554703102</v>
-      </c>
-      <c r="C101">
-        <v>-1520.027314121642</v>
-      </c>
-      <c r="D101">
-        <v>9211.660685878358</v>
-      </c>
-      <c r="E101">
-        <v>4172.688</v>
-      </c>
-      <c r="F101">
-        <v>11534.688</v>
-      </c>
-      <c r="G101">
-        <v>803</v>
-      </c>
-      <c r="H101">
-        <v>4289.2</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2980</v>
-      </c>
-      <c r="K101">
-        <v>1280</v>
-      </c>
-      <c r="L101">
-        <v>1700</v>
-      </c>
-      <c r="M101">
-        <v>1038.12192</v>
-      </c>
-      <c r="N101">
-        <v>661.87808</v>
-      </c>
-      <c r="O101">
-        <v>165.072393152</v>
-      </c>
-      <c r="P101">
-        <v>496.8056868479999</v>
-      </c>
-      <c r="Q101">
-        <v>1776.805686848</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.120520554703102</v>
-      </c>
-      <c r="T101">
-        <v>47.91502435803931</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.2494</v>
-      </c>
-      <c r="W101">
-        <v>0.06755399999999999</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.63757258877647</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
